--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,7312 @@
           <t>Dalaflorans databas</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126344188</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>427801</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6800732</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126343824</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>427890</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6800684</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126345194</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98266</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>427762</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6800755</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126341708</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>427684</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6800496</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126341663</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>427662</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6800508</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126342196</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>427721</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6800575</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126344155</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>427791</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6800750</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126345319</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>427713</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6800676</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126342517</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>427766</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6800601</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126343943</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>427824</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6800763</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126344438</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79566</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>427856</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6800771</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126345366</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>427713</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6800676</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126342845</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>427760</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6800662</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126345835</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>427639</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6800521</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126342458</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>427757</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6800548</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126342376</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>427754</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6800576</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126344176</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>427793</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6800749</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126344538</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>427815</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6800765</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126342811</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>427754</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6800672</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126342873</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>427757</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6800653</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126343564</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>427718</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6800610</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126344191</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>427863</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6800776</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126342209</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>427748</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6800537</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126342782</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>427807</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6800637</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126342716</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>427772</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6800647</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126342493</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>427772</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6800601</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126342894</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>427885</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6800679</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126343893</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>427869</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6800718</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126342666</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>427853</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6800639</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126342911</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79566</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>427855</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6800629</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126342654</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>427849</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6800649</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126343492</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>427849</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6800643</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126341773</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>427709</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6800521</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126342373</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>427751</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6800599</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126342348</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57816</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>427741</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6800571</v>
+      </c>
+      <c r="S37" t="n">
+        <v>50</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126342562</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>427775</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6800618</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126345688</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>427863</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6800776</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126342821</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>427757</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6800667</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126344190</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>427863</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6800769</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126342757</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>427825</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6800599</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126343017</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57653</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>427836</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6800623</v>
+      </c>
+      <c r="S43" t="n">
+        <v>50</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126342702</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>427815</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6800592</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126342854</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>427759</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6800658</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126342984</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>427836</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6800623</v>
+      </c>
+      <c r="S46" t="n">
+        <v>50</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt på en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126345288</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>427716</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6800678</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126342710</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>427850</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6800642</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126342522</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>427776</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6800614</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126342324</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79566</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>427709</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6800521</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126343456</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>427719</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6800632</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126341711</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>427699</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6800501</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126344135</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>427789</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6800775</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126342597</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56848</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>427812</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6800576</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126342643</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>427812</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6800576</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126343089</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>427696</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6800657</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126343852</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>427890</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6800684</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126343538</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>427717</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6800610</v>
+      </c>
+      <c r="S58" t="n">
+        <v>50</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126342704</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>427766</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6800632</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126342934</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>427815</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6800586</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126343866</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>427807</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6800637</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126343534</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>427760</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6800856</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126342537</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>427779</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6800578</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126341797</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>427730</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6800510</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126341728</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>427702</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6800509</v>
+      </c>
+      <c r="S65" t="n">
+        <v>11</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126341731</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>427699</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6800504</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126342856</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>427809</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6800609</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126343713</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>427886</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6800670</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126345275</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>427716</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6800677</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126343269</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>427772</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6800654</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126344155</v>
+        <v>126345319</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,37 +1454,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427791</v>
+        <v>427713</v>
       </c>
       <c r="R9" t="n">
-        <v>6800750</v>
+        <v>6800676</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,22 +1538,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126345319</v>
+        <v>126344155</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,37 +1561,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427713</v>
+        <v>427791</v>
       </c>
       <c r="R10" t="n">
-        <v>6800676</v>
+        <v>6800750</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2299,7 +2299,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126342458</v>
+        <v>126344538</v>
       </c>
       <c r="B17" t="n">
         <v>78977</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427757</v>
+        <v>427815</v>
       </c>
       <c r="R17" t="n">
-        <v>6800548</v>
+        <v>6800765</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2394,19 +2394,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126342376</v>
+        <v>126342811</v>
       </c>
       <c r="B18" t="n">
         <v>78977</v>
@@ -2444,10 +2444,10 @@
         <v>427754</v>
       </c>
       <c r="R18" t="n">
-        <v>6800576</v>
+        <v>6800672</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2501,19 +2501,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126344176</v>
+        <v>126342873</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427793</v>
+        <v>427757</v>
       </c>
       <c r="R19" t="n">
-        <v>6800749</v>
+        <v>6800653</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,19 +2608,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126344538</v>
+        <v>126344176</v>
       </c>
       <c r="B20" t="n">
         <v>78977</v>
@@ -2651,17 +2651,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427815</v>
+        <v>427793</v>
       </c>
       <c r="R20" t="n">
-        <v>6800765</v>
+        <v>6800749</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,19 +2715,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126342811</v>
+        <v>126342376</v>
       </c>
       <c r="B21" t="n">
         <v>78977</v>
@@ -2765,10 +2765,10 @@
         <v>427754</v>
       </c>
       <c r="R21" t="n">
-        <v>6800672</v>
+        <v>6800576</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2822,19 +2822,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126342873</v>
+        <v>126342458</v>
       </c>
       <c r="B22" t="n">
         <v>78977</v>
@@ -2865,14 +2865,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
         <v>427757</v>
       </c>
       <c r="R22" t="n">
-        <v>6800653</v>
+        <v>6800548</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2929,22 +2929,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126343564</v>
+        <v>126342209</v>
       </c>
       <c r="B23" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427718</v>
+        <v>427748</v>
       </c>
       <c r="R23" t="n">
-        <v>6800610</v>
+        <v>6800537</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,22 +3036,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126344191</v>
+        <v>126343564</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427863</v>
+        <v>427718</v>
       </c>
       <c r="R24" t="n">
-        <v>6800776</v>
+        <v>6800610</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3143,22 +3143,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126342209</v>
+        <v>126344191</v>
       </c>
       <c r="B25" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427748</v>
+        <v>427863</v>
       </c>
       <c r="R25" t="n">
-        <v>6800537</v>
+        <v>6800776</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3250,12 +3250,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126342493</v>
+        <v>126343893</v>
       </c>
       <c r="B28" t="n">
         <v>78977</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427772</v>
+        <v>427869</v>
       </c>
       <c r="R28" t="n">
-        <v>6800601</v>
+        <v>6800718</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3571,19 +3571,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126342894</v>
+        <v>126342493</v>
       </c>
       <c r="B29" t="n">
         <v>78977</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427885</v>
+        <v>427772</v>
       </c>
       <c r="R29" t="n">
-        <v>6800679</v>
+        <v>6800601</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3690,7 +3690,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126343893</v>
+        <v>126342894</v>
       </c>
       <c r="B30" t="n">
         <v>78977</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427869</v>
+        <v>427885</v>
       </c>
       <c r="R30" t="n">
-        <v>6800718</v>
+        <v>6800679</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3785,12 +3785,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126341773</v>
+        <v>126345688</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4236,37 +4236,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427709</v>
+        <v>427863</v>
       </c>
       <c r="R35" t="n">
-        <v>6800521</v>
+        <v>6800776</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,22 +4320,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126342373</v>
+        <v>126342821</v>
       </c>
       <c r="B36" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427751</v>
+        <v>427757</v>
       </c>
       <c r="R36" t="n">
-        <v>6800599</v>
+        <v>6800667</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126342348</v>
+        <v>126341773</v>
       </c>
       <c r="B37" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,42 +4450,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427741</v>
+        <v>427709</v>
       </c>
       <c r="R37" t="n">
-        <v>6800571</v>
+        <v>6800521</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4551,10 +4546,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126342562</v>
+        <v>126342373</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,21 +4557,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4586,13 +4581,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427775</v>
+        <v>427751</v>
       </c>
       <c r="R38" t="n">
-        <v>6800618</v>
+        <v>6800599</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4621,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4631,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4646,22 +4641,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126345688</v>
+        <v>126342348</v>
       </c>
       <c r="B39" t="n">
-        <v>78736</v>
+        <v>57816</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4669,37 +4664,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427863</v>
+        <v>427741</v>
       </c>
       <c r="R39" t="n">
-        <v>6800776</v>
+        <v>6800571</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,19 +4753,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126342821</v>
+        <v>126342562</v>
       </c>
       <c r="B40" t="n">
         <v>78977</v>
@@ -4800,13 +4800,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427757</v>
+        <v>427775</v>
       </c>
       <c r="R40" t="n">
-        <v>6800667</v>
+        <v>6800618</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4860,12 +4860,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -6273,40 +6273,35 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126342597</v>
+        <v>126342643</v>
       </c>
       <c r="B54" t="n">
-        <v>56848</v>
+        <v>79595</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -6385,35 +6380,40 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126342643</v>
+        <v>126342597</v>
       </c>
       <c r="B55" t="n">
-        <v>79595</v>
+        <v>56848</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -6599,10 +6599,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126343852</v>
+        <v>126342704</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6610,21 +6610,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427890</v>
+        <v>427766</v>
       </c>
       <c r="R57" t="n">
-        <v>6800684</v>
+        <v>6800632</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6694,19 +6694,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126343538</v>
+        <v>126342934</v>
       </c>
       <c r="B58" t="n">
         <v>78977</v>
@@ -6737,17 +6737,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427717</v>
+        <v>427815</v>
       </c>
       <c r="R58" t="n">
-        <v>6800610</v>
+        <v>6800586</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6786,12 +6786,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6806,22 +6801,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126342704</v>
+        <v>126343852</v>
       </c>
       <c r="B59" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6829,21 +6824,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6853,10 +6848,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427766</v>
+        <v>427890</v>
       </c>
       <c r="R59" t="n">
-        <v>6800632</v>
+        <v>6800684</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6888,7 +6883,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6898,7 +6893,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6913,19 +6908,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126342934</v>
+        <v>126343538</v>
       </c>
       <c r="B60" t="n">
         <v>78977</v>
@@ -6956,17 +6951,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427815</v>
+        <v>427717</v>
       </c>
       <c r="R60" t="n">
-        <v>6800586</v>
+        <v>6800610</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6995,7 +6990,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7005,7 +7000,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7020,12 +7020,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7353,7 +7353,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126341797</v>
+        <v>126343713</v>
       </c>
       <c r="B64" t="n">
         <v>78977</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427730</v>
+        <v>427886</v>
       </c>
       <c r="R64" t="n">
-        <v>6800510</v>
+        <v>6800670</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7448,19 +7448,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126341728</v>
+        <v>126345275</v>
       </c>
       <c r="B65" t="n">
         <v>78736</v>
@@ -7495,13 +7495,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427702</v>
+        <v>427716</v>
       </c>
       <c r="R65" t="n">
-        <v>6800509</v>
+        <v>6800677</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7555,19 +7555,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126341731</v>
+        <v>126341797</v>
       </c>
       <c r="B66" t="n">
         <v>78977</v>
@@ -7598,17 +7598,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427699</v>
+        <v>427730</v>
       </c>
       <c r="R66" t="n">
-        <v>6800504</v>
+        <v>6800510</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7662,22 +7662,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126342856</v>
+        <v>126341728</v>
       </c>
       <c r="B67" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,37 +7685,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427809</v>
+        <v>427702</v>
       </c>
       <c r="R67" t="n">
-        <v>6800609</v>
+        <v>6800509</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7769,19 +7769,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126343713</v>
+        <v>126341731</v>
       </c>
       <c r="B68" t="n">
         <v>78977</v>
@@ -7812,17 +7812,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427886</v>
+        <v>427699</v>
       </c>
       <c r="R68" t="n">
-        <v>6800670</v>
+        <v>6800504</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7876,22 +7876,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126345275</v>
+        <v>126342856</v>
       </c>
       <c r="B69" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7899,37 +7899,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427716</v>
+        <v>427809</v>
       </c>
       <c r="R69" t="n">
-        <v>6800677</v>
+        <v>6800609</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7983,12 +7983,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8105,6 +8105,2700 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126360700</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>427557</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6800970</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126360801</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>427557</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6800830</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126360385</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>427361</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6800820</v>
+      </c>
+      <c r="S73" t="n">
+        <v>14</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126361060</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>427484</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6800811</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126360889</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>427541</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6800793</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126360875</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>427539</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6800795</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126361734</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>427347</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6800742</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126361315</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>427288</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6800772</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126360788</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>427556</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6800830</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126361390</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>427302</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6800790</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126361112</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>427487</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6800706</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126360863</v>
+      </c>
+      <c r="B82" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>427538</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6800796</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126361852</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>427295</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6800821</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126361386</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>427563</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6800720</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126361581</v>
+      </c>
+      <c r="B85" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>427551</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6800729</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126360404</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>427340</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6800812</v>
+      </c>
+      <c r="S86" t="n">
+        <v>14</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126360684</v>
+      </c>
+      <c r="B87" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>427458</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6800813</v>
+      </c>
+      <c r="S87" t="n">
+        <v>15</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126361266</v>
+      </c>
+      <c r="B88" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>427277</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6800807</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126360827</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>427455</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6800844</v>
+      </c>
+      <c r="S89" t="n">
+        <v>9</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126360712</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>427484</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6800811</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126361237</v>
+      </c>
+      <c r="B91" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>427523</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6800730</v>
+      </c>
+      <c r="S91" t="n">
+        <v>15</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Spridda ex i fuktstråken.</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126361794</v>
+      </c>
+      <c r="B92" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>427327</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6800755</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126361181</v>
+      </c>
+      <c r="B93" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>427489</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6800696</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126360931</v>
+      </c>
+      <c r="B94" t="n">
+        <v>98386</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>427472</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6800743</v>
+      </c>
+      <c r="S94" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126360881</v>
+      </c>
+      <c r="B95" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>427452</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6800778</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126344188</v>
+        <v>126341708</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427801</v>
+        <v>427684</v>
       </c>
       <c r="R3" t="n">
-        <v>6800732</v>
+        <v>6800496</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,44 +896,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126343824</v>
+        <v>126345194</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427890</v>
+        <v>427762</v>
       </c>
       <c r="R4" t="n">
-        <v>6800684</v>
+        <v>6800755</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,44 +1003,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126345194</v>
+        <v>126344188</v>
       </c>
       <c r="B5" t="n">
-        <v>98266</v>
+        <v>78736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427762</v>
+        <v>427801</v>
       </c>
       <c r="R5" t="n">
-        <v>6800755</v>
+        <v>6800732</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,22 +1110,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126341708</v>
+        <v>126343824</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,37 +1133,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427684</v>
+        <v>427890</v>
       </c>
       <c r="R6" t="n">
-        <v>6800496</v>
+        <v>6800684</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,12 +1217,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126345319</v>
+        <v>126344155</v>
       </c>
       <c r="B9" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,37 +1454,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427713</v>
+        <v>427791</v>
       </c>
       <c r="R9" t="n">
-        <v>6800676</v>
+        <v>6800750</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,22 +1538,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126344155</v>
+        <v>126345319</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,37 +1561,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427791</v>
+        <v>427713</v>
       </c>
       <c r="R10" t="n">
-        <v>6800750</v>
+        <v>6800676</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,19 +1645,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126342517</v>
+        <v>126342845</v>
       </c>
       <c r="B11" t="n">
         <v>78977</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427766</v>
+        <v>427760</v>
       </c>
       <c r="R11" t="n">
-        <v>6800601</v>
+        <v>6800662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,22 +1752,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126343943</v>
+        <v>126345835</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427824</v>
+        <v>427639</v>
       </c>
       <c r="R12" t="n">
-        <v>6800763</v>
+        <v>6800521</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,22 +1859,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126344438</v>
+        <v>126342517</v>
       </c>
       <c r="B13" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1882,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427856</v>
+        <v>427766</v>
       </c>
       <c r="R13" t="n">
-        <v>6800771</v>
+        <v>6800601</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1978,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126345366</v>
+        <v>126343943</v>
       </c>
       <c r="B14" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,37 +1989,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427713</v>
+        <v>427824</v>
       </c>
       <c r="R14" t="n">
-        <v>6800676</v>
+        <v>6800763</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,22 +2073,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126342845</v>
+        <v>126345366</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,34 +2096,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427760</v>
+        <v>427713</v>
       </c>
       <c r="R15" t="n">
-        <v>6800662</v>
+        <v>6800676</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,22 +2180,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126345835</v>
+        <v>126344438</v>
       </c>
       <c r="B16" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,37 +2203,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427639</v>
+        <v>427856</v>
       </c>
       <c r="R16" t="n">
-        <v>6800521</v>
+        <v>6800771</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,19 +2287,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126344538</v>
+        <v>126342873</v>
       </c>
       <c r="B17" t="n">
         <v>78977</v>
@@ -2330,14 +2330,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427815</v>
+        <v>427757</v>
       </c>
       <c r="R17" t="n">
-        <v>6800765</v>
+        <v>6800653</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2394,19 +2394,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126342811</v>
+        <v>126342458</v>
       </c>
       <c r="B18" t="n">
         <v>78977</v>
@@ -2437,14 +2437,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427754</v>
+        <v>427757</v>
       </c>
       <c r="R18" t="n">
-        <v>6800672</v>
+        <v>6800548</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2501,19 +2501,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126342873</v>
+        <v>126344176</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427757</v>
+        <v>427793</v>
       </c>
       <c r="R19" t="n">
-        <v>6800653</v>
+        <v>6800749</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,19 +2608,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126344176</v>
+        <v>126342811</v>
       </c>
       <c r="B20" t="n">
         <v>78977</v>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427793</v>
+        <v>427754</v>
       </c>
       <c r="R20" t="n">
-        <v>6800749</v>
+        <v>6800672</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,12 +2715,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126342458</v>
+        <v>126344538</v>
       </c>
       <c r="B22" t="n">
         <v>78977</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427757</v>
+        <v>427815</v>
       </c>
       <c r="R22" t="n">
-        <v>6800548</v>
+        <v>6800765</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2929,22 +2929,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126342209</v>
+        <v>126342716</v>
       </c>
       <c r="B23" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427748</v>
+        <v>427772</v>
       </c>
       <c r="R23" t="n">
-        <v>6800537</v>
+        <v>6800647</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,12 +3036,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126342782</v>
+        <v>126342209</v>
       </c>
       <c r="B26" t="n">
         <v>78736</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427807</v>
+        <v>427748</v>
       </c>
       <c r="R26" t="n">
-        <v>6800637</v>
+        <v>6800537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,10 +3369,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126342716</v>
+        <v>126342782</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3404,13 +3404,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427772</v>
+        <v>427807</v>
       </c>
       <c r="R27" t="n">
-        <v>6800647</v>
+        <v>6800637</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3464,12 +3464,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126342493</v>
+        <v>126342894</v>
       </c>
       <c r="B29" t="n">
         <v>78977</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427772</v>
+        <v>427885</v>
       </c>
       <c r="R29" t="n">
-        <v>6800601</v>
+        <v>6800679</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3690,7 +3690,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126342894</v>
+        <v>126342493</v>
       </c>
       <c r="B30" t="n">
         <v>78977</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427885</v>
+        <v>427772</v>
       </c>
       <c r="R30" t="n">
-        <v>6800679</v>
+        <v>6800601</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3797,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126342666</v>
+        <v>126343492</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427853</v>
+        <v>427849</v>
       </c>
       <c r="R31" t="n">
-        <v>6800639</v>
+        <v>6800643</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3892,22 +3892,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126342911</v>
+        <v>126342666</v>
       </c>
       <c r="B32" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3939,13 +3939,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427855</v>
+        <v>427853</v>
       </c>
       <c r="R32" t="n">
-        <v>6800629</v>
+        <v>6800639</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3999,12 +3999,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4118,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126343492</v>
+        <v>126342911</v>
       </c>
       <c r="B34" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,13 +4153,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427849</v>
+        <v>427855</v>
       </c>
       <c r="R34" t="n">
-        <v>6800643</v>
+        <v>6800629</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,22 +4213,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126345688</v>
+        <v>126342821</v>
       </c>
       <c r="B35" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4236,21 +4236,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4260,13 +4260,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427863</v>
+        <v>427757</v>
       </c>
       <c r="R35" t="n">
-        <v>6800776</v>
+        <v>6800667</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,19 +4320,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126342821</v>
+        <v>126341773</v>
       </c>
       <c r="B36" t="n">
         <v>78977</v>
@@ -4363,14 +4363,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427757</v>
+        <v>427709</v>
       </c>
       <c r="R36" t="n">
-        <v>6800667</v>
+        <v>6800521</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,22 +4427,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126341773</v>
+        <v>126342373</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,34 +4450,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427709</v>
+        <v>427751</v>
       </c>
       <c r="R37" t="n">
-        <v>6800521</v>
+        <v>6800599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,22 +4534,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126342373</v>
+        <v>126342562</v>
       </c>
       <c r="B38" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4581,13 +4581,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427751</v>
+        <v>427775</v>
       </c>
       <c r="R38" t="n">
-        <v>6800599</v>
+        <v>6800618</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4641,12 +4641,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126342562</v>
+        <v>126345688</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,21 +4776,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4800,13 +4800,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427775</v>
+        <v>427863</v>
       </c>
       <c r="R40" t="n">
-        <v>6800618</v>
+        <v>6800776</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4860,12 +4860,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126343017</v>
+        <v>126342702</v>
       </c>
       <c r="B43" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5097,42 +5097,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427836</v>
+        <v>427815</v>
       </c>
       <c r="R43" t="n">
-        <v>6800623</v>
+        <v>6800592</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5198,10 +5193,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126342702</v>
+        <v>126343017</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5209,37 +5204,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427815</v>
+        <v>427836</v>
       </c>
       <c r="R44" t="n">
-        <v>6800592</v>
+        <v>6800623</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5524,10 +5524,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126345288</v>
+        <v>126342721</v>
       </c>
       <c r="B47" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427716</v>
+        <v>427850</v>
       </c>
       <c r="R47" t="n">
-        <v>6800678</v>
+        <v>6800642</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5631,10 +5631,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126342710</v>
+        <v>126345288</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427850</v>
+        <v>427716</v>
       </c>
       <c r="R48" t="n">
-        <v>6800642</v>
+        <v>6800678</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5738,10 +5738,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126342522</v>
+        <v>126342324</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,34 +5749,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427776</v>
+        <v>427709</v>
       </c>
       <c r="R49" t="n">
-        <v>6800614</v>
+        <v>6800521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5833,22 +5833,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126342324</v>
+        <v>126342522</v>
       </c>
       <c r="B50" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5856,34 +5856,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427709</v>
+        <v>427776</v>
       </c>
       <c r="R50" t="n">
-        <v>6800521</v>
+        <v>6800614</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5940,12 +5940,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6273,35 +6273,40 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126342643</v>
+        <v>126342597</v>
       </c>
       <c r="B54" t="n">
-        <v>79595</v>
+        <v>56848</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -6380,40 +6385,35 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126342597</v>
+        <v>126342643</v>
       </c>
       <c r="B55" t="n">
-        <v>56848</v>
+        <v>79595</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -6599,10 +6599,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126342704</v>
+        <v>126343852</v>
       </c>
       <c r="B57" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6610,21 +6610,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427766</v>
+        <v>427890</v>
       </c>
       <c r="R57" t="n">
-        <v>6800632</v>
+        <v>6800684</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6694,22 +6694,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126342934</v>
+        <v>126342704</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,13 +6741,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427815</v>
+        <v>427766</v>
       </c>
       <c r="R58" t="n">
-        <v>6800586</v>
+        <v>6800632</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6801,19 +6801,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126343852</v>
+        <v>126342934</v>
       </c>
       <c r="B59" t="n">
         <v>78977</v>
@@ -6848,13 +6848,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427890</v>
+        <v>427815</v>
       </c>
       <c r="R59" t="n">
-        <v>6800684</v>
+        <v>6800586</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6908,12 +6908,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126343534</v>
+        <v>126342537</v>
       </c>
       <c r="B62" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,34 +7150,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427760</v>
+        <v>427779</v>
       </c>
       <c r="R62" t="n">
-        <v>6800856</v>
+        <v>6800578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7234,22 +7234,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126342537</v>
+        <v>126343534</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7257,34 +7257,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427779</v>
+        <v>427760</v>
       </c>
       <c r="R63" t="n">
-        <v>6800578</v>
+        <v>6800856</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7341,19 +7341,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126343713</v>
+        <v>126341797</v>
       </c>
       <c r="B64" t="n">
         <v>78977</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427886</v>
+        <v>427730</v>
       </c>
       <c r="R64" t="n">
-        <v>6800670</v>
+        <v>6800510</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7448,22 +7448,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126345275</v>
+        <v>126342856</v>
       </c>
       <c r="B65" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7471,37 +7471,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427716</v>
+        <v>427809</v>
       </c>
       <c r="R65" t="n">
-        <v>6800677</v>
+        <v>6800609</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7555,19 +7555,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126341797</v>
+        <v>126341731</v>
       </c>
       <c r="B66" t="n">
         <v>78977</v>
@@ -7598,17 +7598,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427730</v>
+        <v>427699</v>
       </c>
       <c r="R66" t="n">
-        <v>6800510</v>
+        <v>6800504</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7662,22 +7662,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126341728</v>
+        <v>126343713</v>
       </c>
       <c r="B67" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,21 +7685,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7709,13 +7709,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427702</v>
+        <v>427886</v>
       </c>
       <c r="R67" t="n">
-        <v>6800509</v>
+        <v>6800670</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7769,22 +7769,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126341731</v>
+        <v>126345275</v>
       </c>
       <c r="B68" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7792,37 +7792,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427699</v>
+        <v>427716</v>
       </c>
       <c r="R68" t="n">
-        <v>6800504</v>
+        <v>6800677</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7876,22 +7876,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126342856</v>
+        <v>126341728</v>
       </c>
       <c r="B69" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7899,37 +7899,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427809</v>
+        <v>427702</v>
       </c>
       <c r="R69" t="n">
-        <v>6800609</v>
+        <v>6800509</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7983,12 +7983,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126360801</v>
+        <v>126360385</v>
       </c>
       <c r="B72" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8225,21 +8225,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8249,13 +8249,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427557</v>
+        <v>427361</v>
       </c>
       <c r="R72" t="n">
-        <v>6800830</v>
+        <v>6800820</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8309,22 +8309,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126360385</v>
+        <v>126360801</v>
       </c>
       <c r="B73" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8332,21 +8332,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8356,13 +8356,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427361</v>
+        <v>427557</v>
       </c>
       <c r="R73" t="n">
-        <v>6800820</v>
+        <v>6800830</v>
       </c>
       <c r="S73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8416,12 +8416,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8535,10 +8535,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126360889</v>
+        <v>126361734</v>
       </c>
       <c r="B75" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8546,37 +8546,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427541</v>
+        <v>427347</v>
       </c>
       <c r="R75" t="n">
-        <v>6800793</v>
+        <v>6800742</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8630,19 +8630,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126360875</v>
+        <v>126361315</v>
       </c>
       <c r="B76" t="n">
         <v>78977</v>
@@ -8673,17 +8673,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427539</v>
+        <v>427288</v>
       </c>
       <c r="R76" t="n">
-        <v>6800795</v>
+        <v>6800772</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8737,22 +8737,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126361734</v>
+        <v>126360875</v>
       </c>
       <c r="B77" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8760,37 +8760,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427347</v>
+        <v>427539</v>
       </c>
       <c r="R77" t="n">
-        <v>6800742</v>
+        <v>6800795</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8844,19 +8844,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126361315</v>
+        <v>126360889</v>
       </c>
       <c r="B78" t="n">
         <v>78977</v>
@@ -8887,17 +8887,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427288</v>
+        <v>427541</v>
       </c>
       <c r="R78" t="n">
-        <v>6800772</v>
+        <v>6800793</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8951,19 +8951,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126360788</v>
+        <v>126361390</v>
       </c>
       <c r="B79" t="n">
         <v>78977</v>
@@ -8994,17 +8994,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427556</v>
+        <v>427302</v>
       </c>
       <c r="R79" t="n">
-        <v>6800830</v>
+        <v>6800790</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9058,19 +9058,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126361390</v>
+        <v>126360788</v>
       </c>
       <c r="B80" t="n">
         <v>78977</v>
@@ -9101,17 +9101,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427302</v>
+        <v>427556</v>
       </c>
       <c r="R80" t="n">
-        <v>6800790</v>
+        <v>6800830</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9165,12 +9165,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9819,7 +9819,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126360684</v>
+        <v>126360827</v>
       </c>
       <c r="B87" t="n">
         <v>78977</v>
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427458</v>
+        <v>427455</v>
       </c>
       <c r="R87" t="n">
-        <v>6800813</v>
+        <v>6800844</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9914,12 +9914,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10033,7 +10033,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126360827</v>
+        <v>126360684</v>
       </c>
       <c r="B89" t="n">
         <v>78977</v>
@@ -10068,13 +10068,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427455</v>
+        <v>427458</v>
       </c>
       <c r="R89" t="n">
-        <v>6800844</v>
+        <v>6800813</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10128,12 +10128,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10466,10 +10466,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126361181</v>
+        <v>126360881</v>
       </c>
       <c r="B93" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10477,21 +10477,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10501,13 +10501,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427489</v>
+        <v>427452</v>
       </c>
       <c r="R93" t="n">
-        <v>6800696</v>
+        <v>6800778</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10573,62 +10573,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126360931</v>
+        <v>126361181</v>
       </c>
       <c r="B94" t="n">
-        <v>98386</v>
+        <v>78977</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427472</v>
+        <v>427489</v>
       </c>
       <c r="R94" t="n">
-        <v>6800743</v>
+        <v>6800696</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10657,7 +10643,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10667,7 +10653,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10694,45 +10680,59 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126360881</v>
+        <v>126360931</v>
       </c>
       <c r="B95" t="n">
-        <v>78736</v>
+        <v>98386</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>219874</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427452</v>
+        <v>427472</v>
       </c>
       <c r="R95" t="n">
-        <v>6800778</v>
+        <v>6800743</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10798,6 +10798,3373 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126377468</v>
+      </c>
+      <c r="B96" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>427684</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6800670</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>126377445</v>
+      </c>
+      <c r="B97" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>427899</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6800814</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>126377470</v>
+      </c>
+      <c r="B98" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>427902</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6800821</v>
+      </c>
+      <c r="S98" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>126377448</v>
+      </c>
+      <c r="B99" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>427957</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6800675</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126377504</v>
+      </c>
+      <c r="B100" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>427888</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6800586</v>
+      </c>
+      <c r="S100" t="n">
+        <v>1</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>126377506</v>
+      </c>
+      <c r="B101" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>427746</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6800458</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>126377490</v>
+      </c>
+      <c r="B102" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>427472</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6800778</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>126377499</v>
+      </c>
+      <c r="B103" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>427795</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6800770</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>126377492</v>
+      </c>
+      <c r="B104" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>427382</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6800755</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>126377465</v>
+      </c>
+      <c r="B105" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>427414</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6800705</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>126377419</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>427506</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6800759</v>
+      </c>
+      <c r="S106" t="n">
+        <v>1</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>126377472</v>
+      </c>
+      <c r="B107" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>427787</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6800513</v>
+      </c>
+      <c r="S107" t="n">
+        <v>1</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>126377451</v>
+      </c>
+      <c r="B108" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>427826</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6800582</v>
+      </c>
+      <c r="S108" t="n">
+        <v>1</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>126377450</v>
+      </c>
+      <c r="B109" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>427846</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6800600</v>
+      </c>
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>126377466</v>
+      </c>
+      <c r="B110" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>427351</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6800743</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>126377498</v>
+      </c>
+      <c r="B111" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>427673</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6800658</v>
+      </c>
+      <c r="S111" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>126377497</v>
+      </c>
+      <c r="B112" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>427570</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6800549</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>126377464</v>
+      </c>
+      <c r="B113" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>427424</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6800736</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>126377434</v>
+      </c>
+      <c r="B114" t="n">
+        <v>97236</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>427273</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6800830</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>126377471</v>
+      </c>
+      <c r="B115" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>427949</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6800622</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>126377428</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79566</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>427419</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6800705</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>126342656</v>
+      </c>
+      <c r="B117" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>427767</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6800630</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>126360802</v>
+      </c>
+      <c r="B118" t="n">
+        <v>98386</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>427417</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6800784</v>
+      </c>
+      <c r="S118" t="n">
+        <v>15</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Utöver blommande ex ett stort antal ex med bara blad. I sänka med mycket enbiuskar.</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>126377449</v>
+      </c>
+      <c r="B119" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>427949</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6800622</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>126345158</v>
+      </c>
+      <c r="B120" t="n">
+        <v>98386</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>427763</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6800750</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Betydligt fler blad som vi bedömer vara nattviol men ej blommande ex.</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>126377502</v>
+      </c>
+      <c r="B121" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>427921</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6800830</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>126377503</v>
+      </c>
+      <c r="B122" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>427952</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6800669</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>126377463</v>
+      </c>
+      <c r="B123" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>427474</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6800777</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>126377505</v>
+      </c>
+      <c r="B124" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>427842</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6800596</v>
+      </c>
+      <c r="S124" t="n">
+        <v>1</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>126377489</v>
+      </c>
+      <c r="B125" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>427569</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6800730</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>126377420</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>427481</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6800782</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126377433</v>
+      </c>
+      <c r="B127" t="n">
+        <v>97230</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>427879</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6800844</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126377452</v>
+      </c>
+      <c r="B128" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>427762</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6800465</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>126377491</v>
+      </c>
+      <c r="B129" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>427416</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6800707</v>
+      </c>
+      <c r="S129" t="n">
+        <v>1</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126341708</v>
+        <v>126344188</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427684</v>
+        <v>427801</v>
       </c>
       <c r="R3" t="n">
-        <v>6800496</v>
+        <v>6800732</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,44 +896,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126345194</v>
+        <v>126343824</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427762</v>
+        <v>427890</v>
       </c>
       <c r="R4" t="n">
-        <v>6800755</v>
+        <v>6800684</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,19 +1003,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126344188</v>
+        <v>126341663</v>
       </c>
       <c r="B5" t="n">
         <v>78736</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427801</v>
+        <v>427662</v>
       </c>
       <c r="R5" t="n">
-        <v>6800732</v>
+        <v>6800508</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,22 +1110,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126343824</v>
+        <v>126341708</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,37 +1133,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427890</v>
+        <v>427684</v>
       </c>
       <c r="R6" t="n">
-        <v>6800684</v>
+        <v>6800496</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,44 +1217,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126341663</v>
+        <v>126345194</v>
       </c>
       <c r="B7" t="n">
-        <v>78736</v>
+        <v>98269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427662</v>
+        <v>427762</v>
       </c>
       <c r="R7" t="n">
-        <v>6800508</v>
+        <v>6800755</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1657,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126342845</v>
+        <v>126344438</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,34 +1668,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427760</v>
+        <v>427856</v>
       </c>
       <c r="R11" t="n">
-        <v>6800662</v>
+        <v>6800771</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,22 +1752,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126345835</v>
+        <v>126342845</v>
       </c>
       <c r="B12" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427639</v>
+        <v>427760</v>
       </c>
       <c r="R12" t="n">
-        <v>6800521</v>
+        <v>6800662</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126342517</v>
+        <v>126345835</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,21 +1882,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427766</v>
+        <v>427639</v>
       </c>
       <c r="R13" t="n">
-        <v>6800601</v>
+        <v>6800521</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,19 +1966,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126343943</v>
+        <v>126342517</v>
       </c>
       <c r="B14" t="n">
         <v>78977</v>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427824</v>
+        <v>427766</v>
       </c>
       <c r="R14" t="n">
-        <v>6800763</v>
+        <v>6800601</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,22 +2073,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126345366</v>
+        <v>126343943</v>
       </c>
       <c r="B15" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,37 +2096,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427713</v>
+        <v>427824</v>
       </c>
       <c r="R15" t="n">
-        <v>6800676</v>
+        <v>6800763</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,22 +2180,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126344438</v>
+        <v>126345366</v>
       </c>
       <c r="B16" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,21 +2203,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427856</v>
+        <v>427713</v>
       </c>
       <c r="R16" t="n">
-        <v>6800771</v>
+        <v>6800676</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2941,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126342716</v>
+        <v>126342209</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427772</v>
+        <v>427748</v>
       </c>
       <c r="R23" t="n">
-        <v>6800647</v>
+        <v>6800537</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,22 +3036,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126343564</v>
+        <v>126342782</v>
       </c>
       <c r="B24" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427718</v>
+        <v>427807</v>
       </c>
       <c r="R24" t="n">
-        <v>6800610</v>
+        <v>6800637</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3143,19 +3143,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126344191</v>
+        <v>126342716</v>
       </c>
       <c r="B25" t="n">
         <v>78977</v>
@@ -3190,13 +3190,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427863</v>
+        <v>427772</v>
       </c>
       <c r="R25" t="n">
-        <v>6800776</v>
+        <v>6800647</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3262,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126342209</v>
+        <v>126343564</v>
       </c>
       <c r="B26" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,21 +3273,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427748</v>
+        <v>427718</v>
       </c>
       <c r="R26" t="n">
-        <v>6800537</v>
+        <v>6800610</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3357,22 +3357,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126342782</v>
+        <v>126344191</v>
       </c>
       <c r="B27" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427807</v>
+        <v>427863</v>
       </c>
       <c r="R27" t="n">
-        <v>6800637</v>
+        <v>6800776</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3464,12 +3464,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -5738,10 +5738,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126342324</v>
+        <v>126342522</v>
       </c>
       <c r="B49" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,34 +5749,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427709</v>
+        <v>427776</v>
       </c>
       <c r="R49" t="n">
-        <v>6800521</v>
+        <v>6800614</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5833,22 +5833,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126342522</v>
+        <v>126343456</v>
       </c>
       <c r="B50" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5856,34 +5856,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427776</v>
+        <v>427719</v>
       </c>
       <c r="R50" t="n">
-        <v>6800614</v>
+        <v>6800632</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5940,22 +5940,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126343456</v>
+        <v>126342324</v>
       </c>
       <c r="B51" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5963,21 +5963,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427719</v>
+        <v>427709</v>
       </c>
       <c r="R51" t="n">
-        <v>6800632</v>
+        <v>6800521</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126342537</v>
+        <v>126343534</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,34 +7150,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427779</v>
+        <v>427760</v>
       </c>
       <c r="R62" t="n">
-        <v>6800578</v>
+        <v>6800856</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7234,22 +7234,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126343534</v>
+        <v>126342537</v>
       </c>
       <c r="B63" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7257,34 +7257,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427760</v>
+        <v>427779</v>
       </c>
       <c r="R63" t="n">
-        <v>6800856</v>
+        <v>6800578</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7341,12 +7341,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -10466,10 +10466,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126360881</v>
+        <v>126361181</v>
       </c>
       <c r="B93" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10477,21 +10477,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10501,13 +10501,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427452</v>
+        <v>427489</v>
       </c>
       <c r="R93" t="n">
-        <v>6800778</v>
+        <v>6800696</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10573,48 +10573,62 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126361181</v>
+        <v>126360931</v>
       </c>
       <c r="B94" t="n">
-        <v>78977</v>
+        <v>98386</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427489</v>
+        <v>427472</v>
       </c>
       <c r="R94" t="n">
-        <v>6800696</v>
+        <v>6800743</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10643,7 +10657,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10653,7 +10667,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10680,59 +10694,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126360931</v>
+        <v>126360881</v>
       </c>
       <c r="B95" t="n">
-        <v>98386</v>
+        <v>78736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219874</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427472</v>
+        <v>427452</v>
       </c>
       <c r="R95" t="n">
-        <v>6800743</v>
+        <v>6800778</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -801,32 +801,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126344188</v>
+        <v>126345194</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>98269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427801</v>
+        <v>427762</v>
       </c>
       <c r="R3" t="n">
-        <v>6800732</v>
+        <v>6800755</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,19 +896,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126343824</v>
+        <v>126344188</v>
       </c>
       <c r="B4" t="n">
         <v>78736</v>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427890</v>
+        <v>427801</v>
       </c>
       <c r="R4" t="n">
-        <v>6800684</v>
+        <v>6800732</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,12 +1003,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126341708</v>
+        <v>126343824</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,37 +1133,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427684</v>
+        <v>427890</v>
       </c>
       <c r="R6" t="n">
-        <v>6800496</v>
+        <v>6800684</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,60 +1217,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126345194</v>
+        <v>126341708</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427762</v>
+        <v>427684</v>
       </c>
       <c r="R7" t="n">
-        <v>6800755</v>
+        <v>6800496</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,22 +1324,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126342196</v>
+        <v>126344155</v>
       </c>
       <c r="B8" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427721</v>
+        <v>427791</v>
       </c>
       <c r="R8" t="n">
-        <v>6800575</v>
+        <v>6800750</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,22 +1431,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126344155</v>
+        <v>126342196</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427791</v>
+        <v>427721</v>
       </c>
       <c r="R9" t="n">
-        <v>6800750</v>
+        <v>6800575</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,12 +1538,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126344438</v>
+        <v>126342845</v>
       </c>
       <c r="B11" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,34 +1668,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427856</v>
+        <v>427760</v>
       </c>
       <c r="R11" t="n">
-        <v>6800771</v>
+        <v>6800662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,19 +1752,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126342845</v>
+        <v>126342517</v>
       </c>
       <c r="B12" t="n">
         <v>78977</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427760</v>
+        <v>427766</v>
       </c>
       <c r="R12" t="n">
-        <v>6800662</v>
+        <v>6800601</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,22 +1859,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126345835</v>
+        <v>126343943</v>
       </c>
       <c r="B13" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,21 +1882,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427639</v>
+        <v>427824</v>
       </c>
       <c r="R13" t="n">
-        <v>6800521</v>
+        <v>6800763</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,22 +1966,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126342517</v>
+        <v>126345835</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,21 +1989,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427766</v>
+        <v>427639</v>
       </c>
       <c r="R14" t="n">
-        <v>6800601</v>
+        <v>6800521</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,22 +2073,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126343943</v>
+        <v>126345366</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,37 +2096,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427824</v>
+        <v>427713</v>
       </c>
       <c r="R15" t="n">
-        <v>6800763</v>
+        <v>6800676</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,22 +2180,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126345366</v>
+        <v>126344438</v>
       </c>
       <c r="B16" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,21 +2203,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427713</v>
+        <v>427856</v>
       </c>
       <c r="R16" t="n">
-        <v>6800676</v>
+        <v>6800771</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2299,7 +2299,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126342873</v>
+        <v>126342811</v>
       </c>
       <c r="B17" t="n">
         <v>78977</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427757</v>
+        <v>427754</v>
       </c>
       <c r="R17" t="n">
-        <v>6800653</v>
+        <v>6800672</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,7 +2406,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126342458</v>
+        <v>126342376</v>
       </c>
       <c r="B18" t="n">
         <v>78977</v>
@@ -2437,17 +2437,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427757</v>
+        <v>427754</v>
       </c>
       <c r="R18" t="n">
-        <v>6800548</v>
+        <v>6800576</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2501,19 +2501,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126344176</v>
+        <v>126344538</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2544,17 +2544,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427793</v>
+        <v>427815</v>
       </c>
       <c r="R19" t="n">
-        <v>6800749</v>
+        <v>6800765</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,19 +2608,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126342811</v>
+        <v>126342873</v>
       </c>
       <c r="B20" t="n">
         <v>78977</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427754</v>
+        <v>427757</v>
       </c>
       <c r="R20" t="n">
-        <v>6800672</v>
+        <v>6800653</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2727,7 +2727,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126342376</v>
+        <v>126342458</v>
       </c>
       <c r="B21" t="n">
         <v>78977</v>
@@ -2758,17 +2758,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427754</v>
+        <v>427757</v>
       </c>
       <c r="R21" t="n">
-        <v>6800576</v>
+        <v>6800548</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2822,19 +2822,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126344538</v>
+        <v>126344176</v>
       </c>
       <c r="B22" t="n">
         <v>78977</v>
@@ -2865,17 +2865,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427815</v>
+        <v>427793</v>
       </c>
       <c r="R22" t="n">
-        <v>6800765</v>
+        <v>6800749</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2929,22 +2929,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126342209</v>
+        <v>126342716</v>
       </c>
       <c r="B23" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427748</v>
+        <v>427772</v>
       </c>
       <c r="R23" t="n">
-        <v>6800537</v>
+        <v>6800647</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,22 +3036,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126342782</v>
+        <v>126344191</v>
       </c>
       <c r="B24" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427807</v>
+        <v>427863</v>
       </c>
       <c r="R24" t="n">
-        <v>6800637</v>
+        <v>6800776</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3143,22 +3143,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126342716</v>
+        <v>126343564</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3190,13 +3190,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427772</v>
+        <v>427718</v>
       </c>
       <c r="R25" t="n">
-        <v>6800647</v>
+        <v>6800610</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3250,22 +3250,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126343564</v>
+        <v>126342209</v>
       </c>
       <c r="B26" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,21 +3273,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427718</v>
+        <v>427748</v>
       </c>
       <c r="R26" t="n">
-        <v>6800610</v>
+        <v>6800537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3357,22 +3357,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126344191</v>
+        <v>126342782</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427863</v>
+        <v>427807</v>
       </c>
       <c r="R27" t="n">
-        <v>6800776</v>
+        <v>6800637</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3464,12 +3464,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126343492</v>
+        <v>126342911</v>
       </c>
       <c r="B31" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427849</v>
+        <v>427855</v>
       </c>
       <c r="R31" t="n">
-        <v>6800643</v>
+        <v>6800629</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3892,12 +3892,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4118,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126342911</v>
+        <v>126343492</v>
       </c>
       <c r="B34" t="n">
-        <v>79566</v>
+        <v>78735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,13 +4153,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427855</v>
+        <v>427849</v>
       </c>
       <c r="R34" t="n">
-        <v>6800629</v>
+        <v>6800643</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,12 +4213,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126342373</v>
+        <v>126342562</v>
       </c>
       <c r="B37" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,21 +4450,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427751</v>
+        <v>427775</v>
       </c>
       <c r="R37" t="n">
-        <v>6800599</v>
+        <v>6800618</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,22 +4534,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126342562</v>
+        <v>126345688</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4581,13 +4581,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427775</v>
+        <v>427863</v>
       </c>
       <c r="R38" t="n">
-        <v>6800618</v>
+        <v>6800776</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4641,22 +4641,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126342348</v>
+        <v>126342373</v>
       </c>
       <c r="B39" t="n">
-        <v>57816</v>
+        <v>79595</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,42 +4664,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427741</v>
+        <v>427751</v>
       </c>
       <c r="R39" t="n">
-        <v>6800571</v>
+        <v>6800599</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4728,7 +4723,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4738,7 +4733,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,22 +4748,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126345688</v>
+        <v>126342348</v>
       </c>
       <c r="B40" t="n">
-        <v>78736</v>
+        <v>57816</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,37 +4771,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427863</v>
+        <v>427741</v>
       </c>
       <c r="R40" t="n">
-        <v>6800776</v>
+        <v>6800571</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4860,19 +4860,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126344190</v>
+        <v>126342757</v>
       </c>
       <c r="B41" t="n">
         <v>78736</v>
@@ -4903,14 +4903,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427863</v>
+        <v>427825</v>
       </c>
       <c r="R41" t="n">
-        <v>6800769</v>
+        <v>6800599</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4967,19 +4967,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126342757</v>
+        <v>126344190</v>
       </c>
       <c r="B42" t="n">
         <v>78736</v>
@@ -5010,14 +5010,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427825</v>
+        <v>427863</v>
       </c>
       <c r="R42" t="n">
-        <v>6800599</v>
+        <v>6800769</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5074,22 +5074,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126342702</v>
+        <v>126343017</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5097,37 +5097,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427815</v>
+        <v>427836</v>
       </c>
       <c r="R43" t="n">
-        <v>6800592</v>
+        <v>6800623</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5193,10 +5198,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126343017</v>
+        <v>126342702</v>
       </c>
       <c r="B44" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5204,42 +5209,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427836</v>
+        <v>427815</v>
       </c>
       <c r="R44" t="n">
-        <v>6800623</v>
+        <v>6800592</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126342721</v>
+        <v>126342710</v>
       </c>
       <c r="B47" t="n">
         <v>78977</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6059,10 +6059,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126341711</v>
+        <v>126344135</v>
       </c>
       <c r="B52" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6070,21 +6070,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6094,13 +6094,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427699</v>
+        <v>427789</v>
       </c>
       <c r="R52" t="n">
-        <v>6800501</v>
+        <v>6800775</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6154,22 +6154,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126344135</v>
+        <v>126341711</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6177,21 +6177,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6201,13 +6201,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427789</v>
+        <v>427699</v>
       </c>
       <c r="R53" t="n">
-        <v>6800775</v>
+        <v>6800501</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6261,12 +6261,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126342704</v>
+        <v>126342934</v>
       </c>
       <c r="B58" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,13 +6741,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427766</v>
+        <v>427815</v>
       </c>
       <c r="R58" t="n">
-        <v>6800632</v>
+        <v>6800586</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6801,19 +6801,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126342934</v>
+        <v>126343538</v>
       </c>
       <c r="B59" t="n">
         <v>78977</v>
@@ -6844,17 +6844,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427815</v>
+        <v>427717</v>
       </c>
       <c r="R59" t="n">
-        <v>6800586</v>
+        <v>6800610</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6893,7 +6893,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6908,22 +6913,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126343538</v>
+        <v>126342704</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6931,37 +6936,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427717</v>
+        <v>427766</v>
       </c>
       <c r="R60" t="n">
-        <v>6800610</v>
+        <v>6800632</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6990,7 +6995,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7000,12 +7005,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7020,22 +7020,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126343866</v>
+        <v>126343534</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7043,21 +7043,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427807</v>
+        <v>427760</v>
       </c>
       <c r="R61" t="n">
-        <v>6800637</v>
+        <v>6800856</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7127,22 +7127,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126343534</v>
+        <v>126343866</v>
       </c>
       <c r="B62" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,21 +7150,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427760</v>
+        <v>427807</v>
       </c>
       <c r="R62" t="n">
-        <v>6800856</v>
+        <v>6800637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7234,12 +7234,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -10466,10 +10466,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126361181</v>
+        <v>126360881</v>
       </c>
       <c r="B93" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10477,21 +10477,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10501,13 +10501,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427489</v>
+        <v>427452</v>
       </c>
       <c r="R93" t="n">
-        <v>6800696</v>
+        <v>6800778</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10573,62 +10573,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126360931</v>
+        <v>126361181</v>
       </c>
       <c r="B94" t="n">
-        <v>98386</v>
+        <v>78977</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427472</v>
+        <v>427489</v>
       </c>
       <c r="R94" t="n">
-        <v>6800743</v>
+        <v>6800696</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10657,7 +10643,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10667,7 +10653,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10694,45 +10680,59 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126360881</v>
+        <v>126360931</v>
       </c>
       <c r="B95" t="n">
-        <v>78736</v>
+        <v>98386</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>219874</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427452</v>
+        <v>427472</v>
       </c>
       <c r="R95" t="n">
-        <v>6800778</v>
+        <v>6800743</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10898,10 +10898,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126377445</v>
+        <v>126377470</v>
       </c>
       <c r="B97" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10909,21 +10909,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10933,10 +10933,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427899</v>
+        <v>427902</v>
       </c>
       <c r="R97" t="n">
-        <v>6800814</v>
+        <v>6800821</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -10995,10 +10995,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126377470</v>
+        <v>126377504</v>
       </c>
       <c r="B98" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11006,21 +11006,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11030,10 +11030,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427902</v>
+        <v>427888</v>
       </c>
       <c r="R98" t="n">
-        <v>6800821</v>
+        <v>6800586</v>
       </c>
       <c r="S98" t="n">
         <v>1</v>
@@ -11092,7 +11092,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126377448</v>
+        <v>126377445</v>
       </c>
       <c r="B99" t="n">
         <v>78736</v>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427957</v>
+        <v>427899</v>
       </c>
       <c r="R99" t="n">
-        <v>6800675</v>
+        <v>6800814</v>
       </c>
       <c r="S99" t="n">
         <v>1</v>
@@ -11189,10 +11189,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126377504</v>
+        <v>126377448</v>
       </c>
       <c r="B100" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11200,21 +11200,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11224,10 +11224,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427888</v>
+        <v>427957</v>
       </c>
       <c r="R100" t="n">
-        <v>6800586</v>
+        <v>6800675</v>
       </c>
       <c r="S100" t="n">
         <v>1</v>
@@ -11577,10 +11577,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126377492</v>
+        <v>126377465</v>
       </c>
       <c r="B104" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11588,21 +11588,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11612,10 +11612,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427382</v>
+        <v>427414</v>
       </c>
       <c r="R104" t="n">
-        <v>6800755</v>
+        <v>6800705</v>
       </c>
       <c r="S104" t="n">
         <v>1</v>
@@ -11674,10 +11674,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126377465</v>
+        <v>126377492</v>
       </c>
       <c r="B105" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11685,21 +11685,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11709,10 +11709,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427414</v>
+        <v>427382</v>
       </c>
       <c r="R105" t="n">
-        <v>6800705</v>
+        <v>6800755</v>
       </c>
       <c r="S105" t="n">
         <v>1</v>
@@ -12644,7 +12644,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126377471</v>
+        <v>126342656</v>
       </c>
       <c r="B115" t="n">
         <v>78735</v>
@@ -12675,17 +12675,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Rytterbygget, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427949</v>
+        <v>427767</v>
       </c>
       <c r="R115" t="n">
-        <v>6800622</v>
+        <v>6800630</v>
       </c>
       <c r="S115" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12712,9 +12712,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12729,22 +12739,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126377428</v>
+        <v>126377471</v>
       </c>
       <c r="B116" t="n">
-        <v>79566</v>
+        <v>78735</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12752,21 +12762,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12776,10 +12786,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427419</v>
+        <v>427949</v>
       </c>
       <c r="R116" t="n">
-        <v>6800705</v>
+        <v>6800622</v>
       </c>
       <c r="S116" t="n">
         <v>1</v>
@@ -12806,12 +12816,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12820,7 +12830,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12839,10 +12848,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126342656</v>
+        <v>126377428</v>
       </c>
       <c r="B117" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12850,37 +12859,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427767</v>
+        <v>427419</v>
       </c>
       <c r="R117" t="n">
-        <v>6800630</v>
+        <v>6800705</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12904,22 +12913,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>17:07</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>17:07</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12928,18 +12927,19 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13877,32 +13877,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126377433</v>
+        <v>126377452</v>
       </c>
       <c r="B127" t="n">
-        <v>97230</v>
+        <v>78736</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13912,10 +13912,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427879</v>
+        <v>427762</v>
       </c>
       <c r="R127" t="n">
-        <v>6800844</v>
+        <v>6800465</v>
       </c>
       <c r="S127" t="n">
         <v>1</v>
@@ -13974,32 +13974,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126377452</v>
+        <v>126377433</v>
       </c>
       <c r="B128" t="n">
-        <v>78736</v>
+        <v>97230</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427762</v>
+        <v>427879</v>
       </c>
       <c r="R128" t="n">
-        <v>6800465</v>
+        <v>6800844</v>
       </c>
       <c r="S128" t="n">
         <v>1</v>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -801,48 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126345194</v>
+        <v>126341708</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427762</v>
+        <v>427684</v>
       </c>
       <c r="R3" t="n">
-        <v>6800755</v>
+        <v>6800496</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,44 +896,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126344188</v>
+        <v>126345194</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427801</v>
+        <v>427762</v>
       </c>
       <c r="R4" t="n">
-        <v>6800732</v>
+        <v>6800755</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,19 +1003,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126341663</v>
+        <v>126344188</v>
       </c>
       <c r="B5" t="n">
         <v>78736</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427662</v>
+        <v>427801</v>
       </c>
       <c r="R5" t="n">
-        <v>6800508</v>
+        <v>6800732</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,19 +1110,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126343824</v>
+        <v>126341663</v>
       </c>
       <c r="B6" t="n">
         <v>78736</v>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427890</v>
+        <v>427662</v>
       </c>
       <c r="R6" t="n">
-        <v>6800684</v>
+        <v>6800508</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,22 +1217,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126341708</v>
+        <v>126343824</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,37 +1240,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427684</v>
+        <v>427890</v>
       </c>
       <c r="R7" t="n">
-        <v>6800496</v>
+        <v>6800684</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,12 +1324,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126345688</v>
+        <v>126342373</v>
       </c>
       <c r="B38" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4581,13 +4581,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427863</v>
+        <v>427751</v>
       </c>
       <c r="R38" t="n">
-        <v>6800776</v>
+        <v>6800599</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4641,22 +4641,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126342373</v>
+        <v>126342348</v>
       </c>
       <c r="B39" t="n">
-        <v>79595</v>
+        <v>57816</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,37 +4664,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427751</v>
+        <v>427741</v>
       </c>
       <c r="R39" t="n">
-        <v>6800599</v>
+        <v>6800571</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4723,7 +4728,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4733,7 +4738,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4748,22 +4753,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126342348</v>
+        <v>126345688</v>
       </c>
       <c r="B40" t="n">
-        <v>57816</v>
+        <v>78736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4771,42 +4776,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427741</v>
+        <v>427863</v>
       </c>
       <c r="R40" t="n">
-        <v>6800571</v>
+        <v>6800776</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4860,12 +4860,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126343017</v>
+        <v>126342702</v>
       </c>
       <c r="B43" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5097,42 +5097,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427836</v>
+        <v>427815</v>
       </c>
       <c r="R43" t="n">
-        <v>6800623</v>
+        <v>6800592</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5198,10 +5193,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126342702</v>
+        <v>126343017</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5209,37 +5204,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427815</v>
+        <v>427836</v>
       </c>
       <c r="R44" t="n">
-        <v>6800592</v>
+        <v>6800623</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126342710</v>
+        <v>126342721</v>
       </c>
       <c r="B47" t="n">
         <v>78977</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5845,10 +5845,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126343456</v>
+        <v>126342324</v>
       </c>
       <c r="B50" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5856,21 +5856,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5880,10 +5880,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427719</v>
+        <v>427709</v>
       </c>
       <c r="R50" t="n">
-        <v>6800632</v>
+        <v>6800521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5952,10 +5952,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126342324</v>
+        <v>126343456</v>
       </c>
       <c r="B51" t="n">
-        <v>79566</v>
+        <v>78735</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5963,21 +5963,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427709</v>
+        <v>427719</v>
       </c>
       <c r="R51" t="n">
-        <v>6800521</v>
+        <v>6800632</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7781,7 +7781,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126345275</v>
+        <v>126341728</v>
       </c>
       <c r="B68" t="n">
         <v>78736</v>
@@ -7816,13 +7816,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427716</v>
+        <v>427702</v>
       </c>
       <c r="R68" t="n">
-        <v>6800677</v>
+        <v>6800509</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7876,19 +7876,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126341728</v>
+        <v>126345275</v>
       </c>
       <c r="B69" t="n">
         <v>78736</v>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427702</v>
+        <v>427716</v>
       </c>
       <c r="R69" t="n">
-        <v>6800509</v>
+        <v>6800677</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7983,12 +7983,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126341708</v>
+        <v>126344188</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427684</v>
+        <v>427801</v>
       </c>
       <c r="R3" t="n">
-        <v>6800496</v>
+        <v>6800732</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,44 +896,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126345194</v>
+        <v>126343824</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>78739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427762</v>
+        <v>427890</v>
       </c>
       <c r="R4" t="n">
-        <v>6800755</v>
+        <v>6800684</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126344188</v>
+        <v>126341663</v>
       </c>
       <c r="B5" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427801</v>
+        <v>427662</v>
       </c>
       <c r="R5" t="n">
-        <v>6800732</v>
+        <v>6800508</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,44 +1110,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126341663</v>
+        <v>126345194</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>98278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427662</v>
+        <v>427762</v>
       </c>
       <c r="R6" t="n">
-        <v>6800508</v>
+        <v>6800755</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126343824</v>
+        <v>126341708</v>
       </c>
       <c r="B7" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,37 +1240,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427890</v>
+        <v>427684</v>
       </c>
       <c r="R7" t="n">
-        <v>6800684</v>
+        <v>6800496</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,12 +1324,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1339,7 +1339,7 @@
         <v>126344155</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>126342196</v>
       </c>
       <c r="B9" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>126345319</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126342845</v>
+        <v>126344438</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>79569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,34 +1668,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427760</v>
+        <v>427856</v>
       </c>
       <c r="R11" t="n">
-        <v>6800662</v>
+        <v>6800771</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,22 +1752,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126342517</v>
+        <v>126345835</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427766</v>
+        <v>427639</v>
       </c>
       <c r="R12" t="n">
-        <v>6800601</v>
+        <v>6800521</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,22 +1859,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126343943</v>
+        <v>126345366</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,37 +1882,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427824</v>
+        <v>427713</v>
       </c>
       <c r="R13" t="n">
-        <v>6800763</v>
+        <v>6800676</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,22 +1966,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126345835</v>
+        <v>126342845</v>
       </c>
       <c r="B14" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,21 +1989,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427639</v>
+        <v>427760</v>
       </c>
       <c r="R14" t="n">
-        <v>6800521</v>
+        <v>6800662</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126345366</v>
+        <v>126342517</v>
       </c>
       <c r="B15" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,34 +2096,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427713</v>
+        <v>427766</v>
       </c>
       <c r="R15" t="n">
-        <v>6800676</v>
+        <v>6800601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126344438</v>
+        <v>126343943</v>
       </c>
       <c r="B16" t="n">
-        <v>79566</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,37 +2203,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427856</v>
+        <v>427824</v>
       </c>
       <c r="R16" t="n">
-        <v>6800771</v>
+        <v>6800762</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,22 +2287,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126342811</v>
+        <v>126344538</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,14 +2330,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427754</v>
+        <v>427815</v>
       </c>
       <c r="R17" t="n">
-        <v>6800672</v>
+        <v>6800765</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2394,22 +2394,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126342376</v>
+        <v>126344176</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427754</v>
+        <v>427793</v>
       </c>
       <c r="R18" t="n">
-        <v>6800576</v>
+        <v>6800749</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126344538</v>
+        <v>126342811</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2544,14 +2544,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427815</v>
+        <v>427754</v>
       </c>
       <c r="R19" t="n">
-        <v>6800765</v>
+        <v>6800672</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,22 +2608,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126342873</v>
+        <v>126342376</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427757</v>
+        <v>427754</v>
       </c>
       <c r="R20" t="n">
-        <v>6800653</v>
+        <v>6800576</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,22 +2715,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126342458</v>
+        <v>126342873</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2758,14 +2758,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
         <v>427757</v>
       </c>
       <c r="R21" t="n">
-        <v>6800548</v>
+        <v>6800653</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2822,22 +2822,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126344176</v>
+        <v>126342458</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,17 +2865,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427793</v>
+        <v>427757</v>
       </c>
       <c r="R22" t="n">
-        <v>6800749</v>
+        <v>6800548</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2929,22 +2929,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126342716</v>
+        <v>126343564</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427772</v>
+        <v>427718</v>
       </c>
       <c r="R23" t="n">
-        <v>6800647</v>
+        <v>6800610</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,22 +3036,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126344191</v>
+        <v>126342716</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,13 +3083,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427863</v>
+        <v>427772</v>
       </c>
       <c r="R24" t="n">
-        <v>6800776</v>
+        <v>6800647</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126343564</v>
+        <v>126344191</v>
       </c>
       <c r="B25" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427718</v>
+        <v>427863</v>
       </c>
       <c r="R25" t="n">
-        <v>6800610</v>
+        <v>6800776</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3250,12 +3250,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3265,7 +3265,7 @@
         <v>126342209</v>
       </c>
       <c r="B26" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>126342782</v>
       </c>
       <c r="B27" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126343893</v>
+        <v>126342894</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427869</v>
+        <v>427885</v>
       </c>
       <c r="R28" t="n">
-        <v>6800718</v>
+        <v>6800679</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3571,22 +3571,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126342894</v>
+        <v>126343893</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427885</v>
+        <v>427869</v>
       </c>
       <c r="R29" t="n">
-        <v>6800679</v>
+        <v>6800718</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3678,12 +3678,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3693,7 +3693,7 @@
         <v>126342493</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>126342911</v>
       </c>
       <c r="B31" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3904,10 +3904,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126342666</v>
+        <v>126343492</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3939,13 +3939,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427853</v>
+        <v>427849</v>
       </c>
       <c r="R32" t="n">
-        <v>6800639</v>
+        <v>6800643</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3999,22 +3999,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126342654</v>
+        <v>126342666</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427849</v>
+        <v>427853</v>
       </c>
       <c r="R33" t="n">
-        <v>6800649</v>
+        <v>6800639</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4118,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126343492</v>
+        <v>126342654</v>
       </c>
       <c r="B34" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         <v>427849</v>
       </c>
       <c r="R34" t="n">
-        <v>6800643</v>
+        <v>6800649</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,22 +4213,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126342821</v>
+        <v>126345688</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4236,21 +4236,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4260,13 +4260,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427757</v>
+        <v>427863</v>
       </c>
       <c r="R35" t="n">
-        <v>6800667</v>
+        <v>6800776</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,22 +4320,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126341773</v>
+        <v>126342373</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,34 +4343,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427709</v>
+        <v>427751</v>
       </c>
       <c r="R36" t="n">
-        <v>6800521</v>
+        <v>6800599</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,22 +4427,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126342562</v>
+        <v>126342821</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427775</v>
+        <v>427757</v>
       </c>
       <c r="R37" t="n">
-        <v>6800618</v>
+        <v>6800667</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,22 +4534,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126342373</v>
+        <v>126341773</v>
       </c>
       <c r="B38" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,34 +4557,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427751</v>
+        <v>427709</v>
       </c>
       <c r="R38" t="n">
-        <v>6800599</v>
+        <v>6800521</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4641,22 +4641,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126342348</v>
+        <v>126342562</v>
       </c>
       <c r="B39" t="n">
-        <v>57816</v>
+        <v>78980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,42 +4664,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427741</v>
+        <v>427775</v>
       </c>
       <c r="R39" t="n">
-        <v>6800571</v>
+        <v>6800618</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4728,7 +4723,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4738,7 +4733,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,22 +4748,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126345688</v>
+        <v>126342348</v>
       </c>
       <c r="B40" t="n">
-        <v>78736</v>
+        <v>57817</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,37 +4771,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427863</v>
+        <v>427741</v>
       </c>
       <c r="R40" t="n">
-        <v>6800776</v>
+        <v>6800571</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4860,22 +4860,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126342757</v>
+        <v>126344190</v>
       </c>
       <c r="B41" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4903,14 +4903,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427825</v>
+        <v>427863</v>
       </c>
       <c r="R41" t="n">
-        <v>6800599</v>
+        <v>6800769</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4967,22 +4967,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126344190</v>
+        <v>126342757</v>
       </c>
       <c r="B42" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5010,14 +5010,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427863</v>
+        <v>427825</v>
       </c>
       <c r="R42" t="n">
-        <v>6800769</v>
+        <v>6800599</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5074,12 +5074,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5089,7 +5089,7 @@
         <v>126342702</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>126343017</v>
       </c>
       <c r="B44" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>126342854</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>126342984</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5524,10 +5524,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126342721</v>
+        <v>126345288</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427850</v>
+        <v>427716</v>
       </c>
       <c r="R47" t="n">
-        <v>6800642</v>
+        <v>6800678</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5631,10 +5631,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126345288</v>
+        <v>126342710</v>
       </c>
       <c r="B48" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427716</v>
+        <v>427850</v>
       </c>
       <c r="R48" t="n">
-        <v>6800678</v>
+        <v>6800642</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5738,10 +5738,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126342522</v>
+        <v>126343456</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,34 +5749,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427776</v>
+        <v>427719</v>
       </c>
       <c r="R49" t="n">
-        <v>6800614</v>
+        <v>6800632</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5833,22 +5833,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126342324</v>
+        <v>126342522</v>
       </c>
       <c r="B50" t="n">
-        <v>79566</v>
+        <v>78980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5856,34 +5856,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427709</v>
+        <v>427776</v>
       </c>
       <c r="R50" t="n">
-        <v>6800521</v>
+        <v>6800614</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5940,22 +5940,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126343456</v>
+        <v>126342324</v>
       </c>
       <c r="B51" t="n">
-        <v>78735</v>
+        <v>79569</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5963,21 +5963,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427719</v>
+        <v>427709</v>
       </c>
       <c r="R51" t="n">
-        <v>6800632</v>
+        <v>6800521</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6059,10 +6059,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126344135</v>
+        <v>126341711</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6070,21 +6070,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6094,13 +6094,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427789</v>
+        <v>427699</v>
       </c>
       <c r="R52" t="n">
-        <v>6800775</v>
+        <v>6800501</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6154,22 +6154,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126341711</v>
+        <v>126344135</v>
       </c>
       <c r="B53" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6177,21 +6177,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6201,13 +6201,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427699</v>
+        <v>427789</v>
       </c>
       <c r="R53" t="n">
-        <v>6800501</v>
+        <v>6800775</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6261,52 +6261,47 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126342597</v>
+        <v>126342643</v>
       </c>
       <c r="B54" t="n">
-        <v>56848</v>
+        <v>79598</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -6385,35 +6380,40 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126342643</v>
+        <v>126342597</v>
       </c>
       <c r="B55" t="n">
-        <v>79595</v>
+        <v>56849</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -6495,7 +6495,7 @@
         <v>126343089</v>
       </c>
       <c r="B56" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6599,10 +6599,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126343852</v>
+        <v>126342934</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6634,13 +6634,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427890</v>
+        <v>427815</v>
       </c>
       <c r="R57" t="n">
-        <v>6800684</v>
+        <v>6800586</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6694,22 +6694,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126342934</v>
+        <v>126343538</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6737,17 +6737,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427815</v>
+        <v>427717</v>
       </c>
       <c r="R58" t="n">
-        <v>6800586</v>
+        <v>6800610</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6786,7 +6786,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6801,22 +6806,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126343538</v>
+        <v>126343852</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6844,17 +6849,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427717</v>
+        <v>427890</v>
       </c>
       <c r="R59" t="n">
-        <v>6800610</v>
+        <v>6800684</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6883,7 +6888,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6893,12 +6898,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6913,12 +6913,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6928,7 +6928,7 @@
         <v>126342704</v>
       </c>
       <c r="B60" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126343534</v>
+        <v>126343866</v>
       </c>
       <c r="B61" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7043,21 +7043,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427760</v>
+        <v>427807</v>
       </c>
       <c r="R61" t="n">
-        <v>6800856</v>
+        <v>6800637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7127,22 +7127,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126343866</v>
+        <v>126342537</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7170,14 +7170,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427807</v>
+        <v>427779</v>
       </c>
       <c r="R62" t="n">
-        <v>6800637</v>
+        <v>6800578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7234,22 +7234,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126342537</v>
+        <v>126343534</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7257,34 +7257,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427779</v>
+        <v>427760</v>
       </c>
       <c r="R63" t="n">
-        <v>6800578</v>
+        <v>6800856</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7341,12 +7341,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7356,7 +7356,7 @@
         <v>126341797</v>
       </c>
       <c r="B64" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>126342856</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>126341731</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>126343713</v>
       </c>
       <c r="B67" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7781,10 +7781,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126341728</v>
+        <v>126345275</v>
       </c>
       <c r="B68" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7816,13 +7816,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427702</v>
+        <v>427716</v>
       </c>
       <c r="R68" t="n">
-        <v>6800509</v>
+        <v>6800677</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7876,22 +7876,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126345275</v>
+        <v>126341728</v>
       </c>
       <c r="B69" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427716</v>
+        <v>427702</v>
       </c>
       <c r="R69" t="n">
-        <v>6800677</v>
+        <v>6800509</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7983,12 +7983,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7998,7 +7998,7 @@
         <v>126343269</v>
       </c>
       <c r="B70" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8107,10 +8107,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126360700</v>
+        <v>126360801</v>
       </c>
       <c r="B71" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8118,21 +8118,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8145,7 +8145,7 @@
         <v>427557</v>
       </c>
       <c r="R71" t="n">
-        <v>6800970</v>
+        <v>6800830</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8214,10 +8214,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126360385</v>
+        <v>126360700</v>
       </c>
       <c r="B72" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8249,13 +8249,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427361</v>
+        <v>427557</v>
       </c>
       <c r="R72" t="n">
-        <v>6800820</v>
+        <v>6800970</v>
       </c>
       <c r="S72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8309,22 +8309,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126360801</v>
+        <v>126360385</v>
       </c>
       <c r="B73" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8332,21 +8332,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8356,13 +8356,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427557</v>
+        <v>427361</v>
       </c>
       <c r="R73" t="n">
-        <v>6800830</v>
+        <v>6800820</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8416,12 +8416,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8431,7 +8431,7 @@
         <v>126361060</v>
       </c>
       <c r="B74" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8535,10 +8535,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126361734</v>
+        <v>126361315</v>
       </c>
       <c r="B75" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8546,21 +8546,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427347</v>
+        <v>427288</v>
       </c>
       <c r="R75" t="n">
-        <v>6800742</v>
+        <v>6800772</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8642,10 +8642,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126361315</v>
+        <v>126360875</v>
       </c>
       <c r="B76" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8673,17 +8673,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427288</v>
+        <v>427539</v>
       </c>
       <c r="R76" t="n">
-        <v>6800772</v>
+        <v>6800795</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8737,22 +8737,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126360875</v>
+        <v>126360889</v>
       </c>
       <c r="B77" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427539</v>
+        <v>427541</v>
       </c>
       <c r="R77" t="n">
-        <v>6800795</v>
+        <v>6800793</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8856,10 +8856,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126360889</v>
+        <v>126361734</v>
       </c>
       <c r="B78" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8867,37 +8867,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427541</v>
+        <v>427347</v>
       </c>
       <c r="R78" t="n">
-        <v>6800793</v>
+        <v>6800742</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8951,12 +8951,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
         <v>126361390</v>
       </c>
       <c r="B79" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>126360788</v>
       </c>
       <c r="B80" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>126361112</v>
       </c>
       <c r="B81" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>126360863</v>
       </c>
       <c r="B82" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>126361852</v>
       </c>
       <c r="B83" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>126361386</v>
       </c>
       <c r="B84" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>126361581</v>
       </c>
       <c r="B85" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>126360404</v>
       </c>
       <c r="B86" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>126360827</v>
       </c>
       <c r="B87" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>126361266</v>
       </c>
       <c r="B88" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>126360684</v>
       </c>
       <c r="B89" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>126360712</v>
       </c>
       <c r="B90" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>126361237</v>
       </c>
       <c r="B91" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>126361794</v>
       </c>
       <c r="B92" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10466,10 +10466,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126360881</v>
+        <v>126361181</v>
       </c>
       <c r="B93" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10477,21 +10477,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10501,13 +10501,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427452</v>
+        <v>427489</v>
       </c>
       <c r="R93" t="n">
-        <v>6800778</v>
+        <v>6800696</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10573,10 +10573,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126361181</v>
+        <v>126360881</v>
       </c>
       <c r="B94" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10584,21 +10584,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10608,13 +10608,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427489</v>
+        <v>427452</v>
       </c>
       <c r="R94" t="n">
-        <v>6800696</v>
+        <v>6800778</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10683,7 +10683,7 @@
         <v>126360931</v>
       </c>
       <c r="B95" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>126377468</v>
       </c>
       <c r="B96" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10898,10 +10898,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126377470</v>
+        <v>126377504</v>
       </c>
       <c r="B97" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10909,21 +10909,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10933,10 +10933,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427902</v>
+        <v>427888</v>
       </c>
       <c r="R97" t="n">
-        <v>6800821</v>
+        <v>6800586</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -10995,10 +10995,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126377504</v>
+        <v>126377470</v>
       </c>
       <c r="B98" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11006,21 +11006,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11030,10 +11030,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427888</v>
+        <v>427902</v>
       </c>
       <c r="R98" t="n">
-        <v>6800586</v>
+        <v>6800821</v>
       </c>
       <c r="S98" t="n">
         <v>1</v>
@@ -11095,7 +11095,7 @@
         <v>126377445</v>
       </c>
       <c r="B99" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>126377448</v>
       </c>
       <c r="B100" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>126377506</v>
       </c>
       <c r="B101" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>126377490</v>
       </c>
       <c r="B102" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>126377499</v>
       </c>
       <c r="B103" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11577,10 +11577,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126377465</v>
+        <v>126377492</v>
       </c>
       <c r="B104" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11588,21 +11588,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11612,10 +11612,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427414</v>
+        <v>427382</v>
       </c>
       <c r="R104" t="n">
-        <v>6800705</v>
+        <v>6800755</v>
       </c>
       <c r="S104" t="n">
         <v>1</v>
@@ -11674,10 +11674,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126377492</v>
+        <v>126377465</v>
       </c>
       <c r="B105" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11685,21 +11685,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11709,10 +11709,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427382</v>
+        <v>427414</v>
       </c>
       <c r="R105" t="n">
-        <v>6800755</v>
+        <v>6800705</v>
       </c>
       <c r="S105" t="n">
         <v>1</v>
@@ -11774,7 +11774,7 @@
         <v>126377419</v>
       </c>
       <c r="B106" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>126377472</v>
       </c>
       <c r="B107" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>126377451</v>
       </c>
       <c r="B108" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>126377450</v>
       </c>
       <c r="B109" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12159,10 +12159,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126377466</v>
+        <v>126377498</v>
       </c>
       <c r="B110" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12170,21 +12170,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12194,10 +12194,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427351</v>
+        <v>427673</v>
       </c>
       <c r="R110" t="n">
-        <v>6800743</v>
+        <v>6800658</v>
       </c>
       <c r="S110" t="n">
         <v>1</v>
@@ -12224,12 +12224,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12256,10 +12256,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126377498</v>
+        <v>126377497</v>
       </c>
       <c r="B111" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12291,10 +12291,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427673</v>
+        <v>427570</v>
       </c>
       <c r="R111" t="n">
-        <v>6800658</v>
+        <v>6800549</v>
       </c>
       <c r="S111" t="n">
         <v>1</v>
@@ -12353,10 +12353,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126377497</v>
+        <v>126377466</v>
       </c>
       <c r="B112" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12364,21 +12364,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12388,10 +12388,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427570</v>
+        <v>427351</v>
       </c>
       <c r="R112" t="n">
-        <v>6800549</v>
+        <v>6800743</v>
       </c>
       <c r="S112" t="n">
         <v>1</v>
@@ -12418,12 +12418,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12453,7 +12453,7 @@
         <v>126377464</v>
       </c>
       <c r="B113" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>126377434</v>
       </c>
       <c r="B114" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12644,10 +12644,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126342656</v>
+        <v>126377471</v>
       </c>
       <c r="B115" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12675,17 +12675,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427767</v>
+        <v>427949</v>
       </c>
       <c r="R115" t="n">
-        <v>6800630</v>
+        <v>6800622</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12712,19 +12712,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>17:07</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12739,22 +12729,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126377471</v>
+        <v>126342656</v>
       </c>
       <c r="B116" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12782,17 +12772,17 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Rytterbygget, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427949</v>
+        <v>427767</v>
       </c>
       <c r="R116" t="n">
-        <v>6800622</v>
+        <v>6800630</v>
       </c>
       <c r="S116" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12819,9 +12809,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12836,60 +12836,74 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126377428</v>
+        <v>126360802</v>
       </c>
       <c r="B117" t="n">
-        <v>79566</v>
+        <v>98395</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>219874</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Rytterbygget, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427419</v>
+        <v>427417</v>
       </c>
       <c r="R117" t="n">
-        <v>6800705</v>
+        <v>6800784</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12916,92 +12930,92 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Utöver blommande ex ett stort antal ex med bara blad. I sänka med mycket enbiuskar.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126360802</v>
+        <v>126377428</v>
       </c>
       <c r="B118" t="n">
-        <v>98386</v>
+        <v>79569</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219874</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427417</v>
+        <v>427419</v>
       </c>
       <c r="R118" t="n">
-        <v>6800784</v>
+        <v>6800705</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13028,44 +13042,30 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Utöver blommande ex ett stort antal ex med bara blad. I sänka med mycket enbiuskar.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -13075,7 +13075,7 @@
         <v>126377449</v>
       </c>
       <c r="B119" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>126345158</v>
       </c>
       <c r="B120" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>126377502</v>
       </c>
       <c r="B121" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>126377503</v>
       </c>
       <c r="B122" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13489,10 +13489,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126377463</v>
+        <v>126377505</v>
       </c>
       <c r="B123" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13500,21 +13500,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13524,10 +13524,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427474</v>
+        <v>427842</v>
       </c>
       <c r="R123" t="n">
-        <v>6800777</v>
+        <v>6800596</v>
       </c>
       <c r="S123" t="n">
         <v>1</v>
@@ -13554,12 +13554,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13586,10 +13586,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126377505</v>
+        <v>126377463</v>
       </c>
       <c r="B124" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13597,21 +13597,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13621,10 +13621,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427842</v>
+        <v>427474</v>
       </c>
       <c r="R124" t="n">
-        <v>6800596</v>
+        <v>6800777</v>
       </c>
       <c r="S124" t="n">
         <v>1</v>
@@ -13651,12 +13651,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13686,7 +13686,7 @@
         <v>126377489</v>
       </c>
       <c r="B125" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>126377420</v>
       </c>
       <c r="B126" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13877,32 +13877,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126377452</v>
+        <v>126377433</v>
       </c>
       <c r="B127" t="n">
-        <v>78736</v>
+        <v>97239</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13912,10 +13912,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427762</v>
+        <v>427879</v>
       </c>
       <c r="R127" t="n">
-        <v>6800465</v>
+        <v>6800844</v>
       </c>
       <c r="S127" t="n">
         <v>1</v>
@@ -13974,32 +13974,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126377433</v>
+        <v>126377452</v>
       </c>
       <c r="B128" t="n">
-        <v>97230</v>
+        <v>78739</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427879</v>
+        <v>427762</v>
       </c>
       <c r="R128" t="n">
-        <v>6800844</v>
+        <v>6800465</v>
       </c>
       <c r="S128" t="n">
         <v>1</v>
@@ -14074,7 +14074,7 @@
         <v>126377491</v>
       </c>
       <c r="B129" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126344155</v>
+        <v>126342196</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427791</v>
+        <v>427721</v>
       </c>
       <c r="R8" t="n">
-        <v>6800750</v>
+        <v>6800575</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,22 +1431,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126342196</v>
+        <v>126344155</v>
       </c>
       <c r="B9" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427721</v>
+        <v>427791</v>
       </c>
       <c r="R9" t="n">
-        <v>6800575</v>
+        <v>6800750</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,12 +1538,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -6273,35 +6273,40 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126342643</v>
+        <v>126342597</v>
       </c>
       <c r="B54" t="n">
-        <v>79598</v>
+        <v>56849</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -6380,40 +6385,35 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126342597</v>
+        <v>126342643</v>
       </c>
       <c r="B55" t="n">
-        <v>56849</v>
+        <v>79598</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -6599,7 +6599,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126342934</v>
+        <v>126343852</v>
       </c>
       <c r="B57" t="n">
         <v>78980</v>
@@ -6634,13 +6634,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427815</v>
+        <v>427890</v>
       </c>
       <c r="R57" t="n">
-        <v>6800586</v>
+        <v>6800684</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6694,22 +6694,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126343538</v>
+        <v>126342704</v>
       </c>
       <c r="B58" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,37 +6717,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427717</v>
+        <v>427766</v>
       </c>
       <c r="R58" t="n">
-        <v>6800610</v>
+        <v>6800632</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6786,12 +6786,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6806,19 +6801,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126343852</v>
+        <v>126342934</v>
       </c>
       <c r="B59" t="n">
         <v>78980</v>
@@ -6853,13 +6848,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427890</v>
+        <v>427815</v>
       </c>
       <c r="R59" t="n">
-        <v>6800684</v>
+        <v>6800586</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6888,7 +6883,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6898,7 +6893,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6913,22 +6908,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126342704</v>
+        <v>126343538</v>
       </c>
       <c r="B60" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6936,37 +6931,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427766</v>
+        <v>427717</v>
       </c>
       <c r="R60" t="n">
-        <v>6800632</v>
+        <v>6800610</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6995,7 +6990,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7005,7 +7000,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7020,22 +7020,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126343866</v>
+        <v>126343534</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7043,21 +7043,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427807</v>
+        <v>427760</v>
       </c>
       <c r="R61" t="n">
-        <v>6800637</v>
+        <v>6800856</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7127,19 +7127,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126342537</v>
+        <v>126343866</v>
       </c>
       <c r="B62" t="n">
         <v>78980</v>
@@ -7170,14 +7170,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427779</v>
+        <v>427807</v>
       </c>
       <c r="R62" t="n">
-        <v>6800578</v>
+        <v>6800637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7234,22 +7234,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126343534</v>
+        <v>126342537</v>
       </c>
       <c r="B63" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7257,34 +7257,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427760</v>
+        <v>427779</v>
       </c>
       <c r="R63" t="n">
-        <v>6800856</v>
+        <v>6800578</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7341,12 +7341,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -10466,48 +10466,62 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126361181</v>
+        <v>126360931</v>
       </c>
       <c r="B93" t="n">
-        <v>78980</v>
+        <v>98395</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427489</v>
+        <v>427472</v>
       </c>
       <c r="R93" t="n">
-        <v>6800696</v>
+        <v>6800743</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10536,7 +10550,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10546,7 +10560,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10680,62 +10694,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126360931</v>
+        <v>126361181</v>
       </c>
       <c r="B95" t="n">
-        <v>98395</v>
+        <v>78980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427472</v>
+        <v>427489</v>
       </c>
       <c r="R95" t="n">
-        <v>6800743</v>
+        <v>6800696</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126344188</v>
+        <v>126341708</v>
       </c>
       <c r="B3" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427801</v>
+        <v>427684</v>
       </c>
       <c r="R3" t="n">
-        <v>6800732</v>
+        <v>6800496</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,44 +896,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126343824</v>
+        <v>126345194</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427890</v>
+        <v>427762</v>
       </c>
       <c r="R4" t="n">
-        <v>6800684</v>
+        <v>6800755</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,19 +1003,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126341663</v>
+        <v>126344188</v>
       </c>
       <c r="B5" t="n">
         <v>78739</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427662</v>
+        <v>427801</v>
       </c>
       <c r="R5" t="n">
-        <v>6800508</v>
+        <v>6800732</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,44 +1110,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126345194</v>
+        <v>126343824</v>
       </c>
       <c r="B6" t="n">
-        <v>98278</v>
+        <v>78739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427762</v>
+        <v>427890</v>
       </c>
       <c r="R6" t="n">
-        <v>6800755</v>
+        <v>6800684</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,22 +1217,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126341708</v>
+        <v>126341663</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427684</v>
+        <v>427662</v>
       </c>
       <c r="R7" t="n">
-        <v>6800496</v>
+        <v>6800508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,12 +1324,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126345835</v>
+        <v>126342845</v>
       </c>
       <c r="B12" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427639</v>
+        <v>427760</v>
       </c>
       <c r="R12" t="n">
-        <v>6800521</v>
+        <v>6800662</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126345366</v>
+        <v>126345835</v>
       </c>
       <c r="B13" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,37 +1882,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427713</v>
+        <v>427639</v>
       </c>
       <c r="R13" t="n">
-        <v>6800676</v>
+        <v>6800521</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,19 +1966,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126342845</v>
+        <v>126342517</v>
       </c>
       <c r="B14" t="n">
         <v>78980</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427760</v>
+        <v>427766</v>
       </c>
       <c r="R14" t="n">
-        <v>6800662</v>
+        <v>6800601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,19 +2073,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126342517</v>
+        <v>126343943</v>
       </c>
       <c r="B15" t="n">
         <v>78980</v>
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427766</v>
+        <v>427824</v>
       </c>
       <c r="R15" t="n">
-        <v>6800601</v>
+        <v>6800762</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,22 +2180,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126343943</v>
+        <v>126345366</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,37 +2203,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427824</v>
+        <v>427713</v>
       </c>
       <c r="R16" t="n">
-        <v>6800762</v>
+        <v>6800676</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,19 +2287,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126344538</v>
+        <v>126344176</v>
       </c>
       <c r="B17" t="n">
         <v>78980</v>
@@ -2330,17 +2330,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427815</v>
+        <v>427793</v>
       </c>
       <c r="R17" t="n">
-        <v>6800765</v>
+        <v>6800749</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2394,19 +2394,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126344176</v>
+        <v>126342811</v>
       </c>
       <c r="B18" t="n">
         <v>78980</v>
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427793</v>
+        <v>427754</v>
       </c>
       <c r="R18" t="n">
-        <v>6800749</v>
+        <v>6800672</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2501,19 +2501,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126342811</v>
+        <v>126342376</v>
       </c>
       <c r="B19" t="n">
         <v>78980</v>
@@ -2551,10 +2551,10 @@
         <v>427754</v>
       </c>
       <c r="R19" t="n">
-        <v>6800672</v>
+        <v>6800576</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,19 +2608,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126342376</v>
+        <v>126344538</v>
       </c>
       <c r="B20" t="n">
         <v>78980</v>
@@ -2651,17 +2651,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427754</v>
+        <v>427815</v>
       </c>
       <c r="R20" t="n">
-        <v>6800576</v>
+        <v>6800765</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,12 +2715,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126343564</v>
+        <v>126342209</v>
       </c>
       <c r="B23" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427718</v>
+        <v>427748</v>
       </c>
       <c r="R23" t="n">
-        <v>6800610</v>
+        <v>6800537</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,22 +3036,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126342716</v>
+        <v>126342782</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,13 +3083,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427772</v>
+        <v>427807</v>
       </c>
       <c r="R24" t="n">
-        <v>6800647</v>
+        <v>6800637</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3143,19 +3143,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126344191</v>
+        <v>126342716</v>
       </c>
       <c r="B25" t="n">
         <v>78980</v>
@@ -3190,13 +3190,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427863</v>
+        <v>427772</v>
       </c>
       <c r="R25" t="n">
-        <v>6800776</v>
+        <v>6800647</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3262,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126342209</v>
+        <v>126343564</v>
       </c>
       <c r="B26" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,21 +3273,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427748</v>
+        <v>427718</v>
       </c>
       <c r="R26" t="n">
-        <v>6800537</v>
+        <v>6800610</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3357,22 +3357,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126342782</v>
+        <v>126344191</v>
       </c>
       <c r="B27" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427807</v>
+        <v>427863</v>
       </c>
       <c r="R27" t="n">
-        <v>6800637</v>
+        <v>6800776</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3464,19 +3464,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126342894</v>
+        <v>126343893</v>
       </c>
       <c r="B28" t="n">
         <v>78980</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427885</v>
+        <v>427869</v>
       </c>
       <c r="R28" t="n">
-        <v>6800679</v>
+        <v>6800718</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3571,19 +3571,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126343893</v>
+        <v>126342894</v>
       </c>
       <c r="B29" t="n">
         <v>78980</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427869</v>
+        <v>427885</v>
       </c>
       <c r="R29" t="n">
-        <v>6800718</v>
+        <v>6800679</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3678,12 +3678,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126342911</v>
+        <v>126343492</v>
       </c>
       <c r="B31" t="n">
-        <v>79569</v>
+        <v>78738</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427855</v>
+        <v>427849</v>
       </c>
       <c r="R31" t="n">
-        <v>6800629</v>
+        <v>6800643</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3892,22 +3892,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126343492</v>
+        <v>126342666</v>
       </c>
       <c r="B32" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3939,13 +3939,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427849</v>
+        <v>427853</v>
       </c>
       <c r="R32" t="n">
-        <v>6800643</v>
+        <v>6800639</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3999,19 +3999,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126342666</v>
+        <v>126342654</v>
       </c>
       <c r="B33" t="n">
         <v>78980</v>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427853</v>
+        <v>427849</v>
       </c>
       <c r="R33" t="n">
-        <v>6800639</v>
+        <v>6800649</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4118,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126342654</v>
+        <v>126342911</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,13 +4153,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427849</v>
+        <v>427855</v>
       </c>
       <c r="R34" t="n">
-        <v>6800649</v>
+        <v>6800629</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,22 +4213,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126345688</v>
+        <v>126342821</v>
       </c>
       <c r="B35" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4236,21 +4236,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4260,13 +4260,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427863</v>
+        <v>427757</v>
       </c>
       <c r="R35" t="n">
-        <v>6800776</v>
+        <v>6800667</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,22 +4320,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126342373</v>
+        <v>126341773</v>
       </c>
       <c r="B36" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,34 +4343,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427751</v>
+        <v>427709</v>
       </c>
       <c r="R36" t="n">
-        <v>6800599</v>
+        <v>6800521</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,22 +4427,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126342821</v>
+        <v>126342373</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,21 +4450,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427757</v>
+        <v>427751</v>
       </c>
       <c r="R37" t="n">
-        <v>6800667</v>
+        <v>6800599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,7 +4546,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126341773</v>
+        <v>126342562</v>
       </c>
       <c r="B38" t="n">
         <v>78980</v>
@@ -4577,17 +4577,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427709</v>
+        <v>427775</v>
       </c>
       <c r="R38" t="n">
-        <v>6800521</v>
+        <v>6800618</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4641,22 +4641,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126342562</v>
+        <v>126342348</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,37 +4664,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427775</v>
+        <v>427741</v>
       </c>
       <c r="R39" t="n">
-        <v>6800618</v>
+        <v>6800571</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4723,7 +4728,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4733,7 +4738,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4748,22 +4753,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126342348</v>
+        <v>126345688</v>
       </c>
       <c r="B40" t="n">
-        <v>57817</v>
+        <v>78739</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4771,42 +4776,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427741</v>
+        <v>427863</v>
       </c>
       <c r="R40" t="n">
-        <v>6800571</v>
+        <v>6800776</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4860,12 +4860,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126345288</v>
+        <v>126342710</v>
       </c>
       <c r="B47" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427716</v>
+        <v>427850</v>
       </c>
       <c r="R47" t="n">
-        <v>6800678</v>
+        <v>6800642</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5631,10 +5631,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126342710</v>
+        <v>126345288</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427850</v>
+        <v>427716</v>
       </c>
       <c r="R48" t="n">
-        <v>6800642</v>
+        <v>6800678</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5738,10 +5738,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126343456</v>
+        <v>126342522</v>
       </c>
       <c r="B49" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,34 +5749,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427719</v>
+        <v>427776</v>
       </c>
       <c r="R49" t="n">
-        <v>6800632</v>
+        <v>6800614</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5833,22 +5833,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126342522</v>
+        <v>126343456</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5856,34 +5856,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427776</v>
+        <v>427719</v>
       </c>
       <c r="R50" t="n">
-        <v>6800614</v>
+        <v>6800632</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5940,12 +5940,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6273,40 +6273,35 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126342597</v>
+        <v>126342643</v>
       </c>
       <c r="B54" t="n">
-        <v>56849</v>
+        <v>79598</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -6385,35 +6380,40 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126342643</v>
+        <v>126342597</v>
       </c>
       <c r="B55" t="n">
-        <v>79598</v>
+        <v>56849</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126343534</v>
+        <v>126343866</v>
       </c>
       <c r="B61" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7043,21 +7043,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427760</v>
+        <v>427807</v>
       </c>
       <c r="R61" t="n">
-        <v>6800856</v>
+        <v>6800637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7127,19 +7127,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126343866</v>
+        <v>126342537</v>
       </c>
       <c r="B62" t="n">
         <v>78980</v>
@@ -7170,14 +7170,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427807</v>
+        <v>427779</v>
       </c>
       <c r="R62" t="n">
-        <v>6800637</v>
+        <v>6800578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7234,22 +7234,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126342537</v>
+        <v>126343534</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7257,34 +7257,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427779</v>
+        <v>427760</v>
       </c>
       <c r="R63" t="n">
-        <v>6800578</v>
+        <v>6800856</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7341,22 +7341,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126341797</v>
+        <v>126345275</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7364,21 +7364,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427730</v>
+        <v>427716</v>
       </c>
       <c r="R64" t="n">
-        <v>6800510</v>
+        <v>6800677</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7448,22 +7448,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126342856</v>
+        <v>126341728</v>
       </c>
       <c r="B65" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7471,37 +7471,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427809</v>
+        <v>427702</v>
       </c>
       <c r="R65" t="n">
-        <v>6800609</v>
+        <v>6800509</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7555,19 +7555,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126341731</v>
+        <v>126341797</v>
       </c>
       <c r="B66" t="n">
         <v>78980</v>
@@ -7598,17 +7598,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427699</v>
+        <v>427730</v>
       </c>
       <c r="R66" t="n">
-        <v>6800504</v>
+        <v>6800510</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7662,19 +7662,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126343713</v>
+        <v>126342856</v>
       </c>
       <c r="B67" t="n">
         <v>78980</v>
@@ -7705,17 +7705,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427886</v>
+        <v>427809</v>
       </c>
       <c r="R67" t="n">
-        <v>6800670</v>
+        <v>6800609</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7769,22 +7769,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126345275</v>
+        <v>126341731</v>
       </c>
       <c r="B68" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7792,37 +7792,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427716</v>
+        <v>427699</v>
       </c>
       <c r="R68" t="n">
-        <v>6800677</v>
+        <v>6800504</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7876,22 +7876,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126341728</v>
+        <v>126343713</v>
       </c>
       <c r="B69" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7899,21 +7899,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427702</v>
+        <v>427886</v>
       </c>
       <c r="R69" t="n">
-        <v>6800509</v>
+        <v>6800670</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7983,12 +7983,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8107,10 +8107,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126360801</v>
+        <v>126360385</v>
       </c>
       <c r="B71" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8118,21 +8118,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8142,13 +8142,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427557</v>
+        <v>427361</v>
       </c>
       <c r="R71" t="n">
-        <v>6800830</v>
+        <v>6800820</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8202,12 +8202,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8321,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126360385</v>
+        <v>126360801</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8332,21 +8332,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8356,13 +8356,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427361</v>
+        <v>427557</v>
       </c>
       <c r="R73" t="n">
-        <v>6800820</v>
+        <v>6800830</v>
       </c>
       <c r="S73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8416,12 +8416,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -10466,59 +10466,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126360931</v>
+        <v>126360881</v>
       </c>
       <c r="B93" t="n">
-        <v>98395</v>
+        <v>78739</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219874</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427472</v>
+        <v>427452</v>
       </c>
       <c r="R93" t="n">
-        <v>6800743</v>
+        <v>6800778</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10550,7 +10536,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10560,7 +10546,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10587,10 +10573,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126360881</v>
+        <v>126361181</v>
       </c>
       <c r="B94" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10598,21 +10584,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10622,13 +10608,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427452</v>
+        <v>427489</v>
       </c>
       <c r="R94" t="n">
-        <v>6800778</v>
+        <v>6800696</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10657,7 +10643,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10667,7 +10653,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10694,48 +10680,62 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126361181</v>
+        <v>126360931</v>
       </c>
       <c r="B95" t="n">
-        <v>78980</v>
+        <v>98395</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427489</v>
+        <v>427472</v>
       </c>
       <c r="R95" t="n">
-        <v>6800696</v>
+        <v>6800743</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10898,10 +10898,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126377504</v>
+        <v>126377470</v>
       </c>
       <c r="B97" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10909,21 +10909,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10933,10 +10933,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427888</v>
+        <v>427902</v>
       </c>
       <c r="R97" t="n">
-        <v>6800586</v>
+        <v>6800821</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -10995,10 +10995,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126377470</v>
+        <v>126377504</v>
       </c>
       <c r="B98" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11006,21 +11006,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11030,10 +11030,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427902</v>
+        <v>427888</v>
       </c>
       <c r="R98" t="n">
-        <v>6800821</v>
+        <v>6800586</v>
       </c>
       <c r="S98" t="n">
         <v>1</v>
@@ -12159,10 +12159,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126377498</v>
+        <v>126377466</v>
       </c>
       <c r="B110" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12170,21 +12170,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12194,10 +12194,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427673</v>
+        <v>427351</v>
       </c>
       <c r="R110" t="n">
-        <v>6800658</v>
+        <v>6800743</v>
       </c>
       <c r="S110" t="n">
         <v>1</v>
@@ -12224,12 +12224,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12256,7 +12256,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126377497</v>
+        <v>126377498</v>
       </c>
       <c r="B111" t="n">
         <v>78980</v>
@@ -12291,10 +12291,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427570</v>
+        <v>427673</v>
       </c>
       <c r="R111" t="n">
-        <v>6800549</v>
+        <v>6800658</v>
       </c>
       <c r="S111" t="n">
         <v>1</v>
@@ -12353,10 +12353,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126377466</v>
+        <v>126377497</v>
       </c>
       <c r="B112" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12364,21 +12364,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12388,10 +12388,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427351</v>
+        <v>427570</v>
       </c>
       <c r="R112" t="n">
-        <v>6800743</v>
+        <v>6800549</v>
       </c>
       <c r="S112" t="n">
         <v>1</v>
@@ -12418,12 +12418,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12644,10 +12644,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126377471</v>
+        <v>126377428</v>
       </c>
       <c r="B115" t="n">
-        <v>78738</v>
+        <v>79569</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12655,21 +12655,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12679,10 +12679,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427949</v>
+        <v>427419</v>
       </c>
       <c r="R115" t="n">
-        <v>6800622</v>
+        <v>6800705</v>
       </c>
       <c r="S115" t="n">
         <v>1</v>
@@ -12709,12 +12709,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12723,6 +12723,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12741,48 +12742,62 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126342656</v>
+        <v>126360802</v>
       </c>
       <c r="B116" t="n">
-        <v>78738</v>
+        <v>98395</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427767</v>
+        <v>427417</v>
       </c>
       <c r="R116" t="n">
-        <v>6800630</v>
+        <v>6800784</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12806,22 +12821,27 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Utöver blommande ex ett stort antal ex med bara blad. I sänka med mycket enbiuskar.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12848,62 +12868,48 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126360802</v>
+        <v>126342656</v>
       </c>
       <c r="B117" t="n">
-        <v>98395</v>
+        <v>78738</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427417</v>
+        <v>427767</v>
       </c>
       <c r="R117" t="n">
-        <v>6800784</v>
+        <v>6800630</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12927,27 +12933,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Utöver blommande ex ett stort antal ex med bara blad. I sänka med mycket enbiuskar.</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12974,10 +12975,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126377428</v>
+        <v>126377471</v>
       </c>
       <c r="B118" t="n">
-        <v>79569</v>
+        <v>78738</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12985,21 +12986,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13009,10 +13010,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427419</v>
+        <v>427949</v>
       </c>
       <c r="R118" t="n">
-        <v>6800705</v>
+        <v>6800622</v>
       </c>
       <c r="S118" t="n">
         <v>1</v>
@@ -13039,12 +13040,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13053,7 +13054,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13489,10 +13489,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126377505</v>
+        <v>126377463</v>
       </c>
       <c r="B123" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13500,21 +13500,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13524,10 +13524,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427842</v>
+        <v>427474</v>
       </c>
       <c r="R123" t="n">
-        <v>6800596</v>
+        <v>6800777</v>
       </c>
       <c r="S123" t="n">
         <v>1</v>
@@ -13554,12 +13554,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13586,10 +13586,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126377463</v>
+        <v>126377505</v>
       </c>
       <c r="B124" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13597,21 +13597,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13621,10 +13621,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427474</v>
+        <v>427842</v>
       </c>
       <c r="R124" t="n">
-        <v>6800777</v>
+        <v>6800596</v>
       </c>
       <c r="S124" t="n">
         <v>1</v>
@@ -13651,12 +13651,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13877,32 +13877,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126377433</v>
+        <v>126377452</v>
       </c>
       <c r="B127" t="n">
-        <v>97239</v>
+        <v>78739</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13912,10 +13912,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427879</v>
+        <v>427762</v>
       </c>
       <c r="R127" t="n">
-        <v>6800844</v>
+        <v>6800465</v>
       </c>
       <c r="S127" t="n">
         <v>1</v>
@@ -13974,32 +13974,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126377452</v>
+        <v>126377433</v>
       </c>
       <c r="B128" t="n">
-        <v>78739</v>
+        <v>97239</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427762</v>
+        <v>427879</v>
       </c>
       <c r="R128" t="n">
-        <v>6800465</v>
+        <v>6800844</v>
       </c>
       <c r="S128" t="n">
         <v>1</v>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126342196</v>
+        <v>126345319</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,34 +1347,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427721</v>
+        <v>427713</v>
       </c>
       <c r="R8" t="n">
-        <v>6800575</v>
+        <v>6800676</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,22 +1431,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126344155</v>
+        <v>126342196</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427791</v>
+        <v>427721</v>
       </c>
       <c r="R9" t="n">
-        <v>6800750</v>
+        <v>6800575</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,22 +1538,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126345319</v>
+        <v>126344155</v>
       </c>
       <c r="B10" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,37 +1561,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427713</v>
+        <v>427791</v>
       </c>
       <c r="R10" t="n">
-        <v>6800676</v>
+        <v>6800750</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -10898,10 +10898,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126377470</v>
+        <v>126377445</v>
       </c>
       <c r="B97" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10909,21 +10909,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10933,10 +10933,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427902</v>
+        <v>427899</v>
       </c>
       <c r="R97" t="n">
-        <v>6800821</v>
+        <v>6800814</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -10995,10 +10995,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126377504</v>
+        <v>126377448</v>
       </c>
       <c r="B98" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11006,21 +11006,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11030,10 +11030,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427888</v>
+        <v>427957</v>
       </c>
       <c r="R98" t="n">
-        <v>6800586</v>
+        <v>6800675</v>
       </c>
       <c r="S98" t="n">
         <v>1</v>
@@ -11092,10 +11092,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126377445</v>
+        <v>126377470</v>
       </c>
       <c r="B99" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11103,21 +11103,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427899</v>
+        <v>427902</v>
       </c>
       <c r="R99" t="n">
-        <v>6800814</v>
+        <v>6800821</v>
       </c>
       <c r="S99" t="n">
         <v>1</v>
@@ -11189,10 +11189,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126377448</v>
+        <v>126377504</v>
       </c>
       <c r="B100" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11200,21 +11200,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11224,10 +11224,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427957</v>
+        <v>427888</v>
       </c>
       <c r="R100" t="n">
-        <v>6800675</v>
+        <v>6800586</v>
       </c>
       <c r="S100" t="n">
         <v>1</v>
@@ -13683,32 +13683,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126377489</v>
+        <v>126377433</v>
       </c>
       <c r="B125" t="n">
-        <v>78980</v>
+        <v>97239</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13718,10 +13718,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427569</v>
+        <v>427879</v>
       </c>
       <c r="R125" t="n">
-        <v>6800730</v>
+        <v>6800844</v>
       </c>
       <c r="S125" t="n">
         <v>1</v>
@@ -13748,12 +13748,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13780,10 +13780,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126377420</v>
+        <v>126377452</v>
       </c>
       <c r="B126" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13791,21 +13791,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,10 +13815,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427481</v>
+        <v>427762</v>
       </c>
       <c r="R126" t="n">
-        <v>6800782</v>
+        <v>6800465</v>
       </c>
       <c r="S126" t="n">
         <v>1</v>
@@ -13845,12 +13845,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13877,10 +13877,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126377452</v>
+        <v>126377420</v>
       </c>
       <c r="B127" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13888,21 +13888,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13912,10 +13912,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427762</v>
+        <v>427481</v>
       </c>
       <c r="R127" t="n">
-        <v>6800465</v>
+        <v>6800782</v>
       </c>
       <c r="S127" t="n">
         <v>1</v>
@@ -13942,12 +13942,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13974,32 +13974,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126377433</v>
+        <v>126377489</v>
       </c>
       <c r="B128" t="n">
-        <v>97239</v>
+        <v>78980</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427879</v>
+        <v>427569</v>
       </c>
       <c r="R128" t="n">
-        <v>6800844</v>
+        <v>6800730</v>
       </c>
       <c r="S128" t="n">
         <v>1</v>
@@ -14039,12 +14039,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD128" t="b">

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126341708</v>
+        <v>126344188</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427684</v>
+        <v>427801</v>
       </c>
       <c r="R3" t="n">
-        <v>6800496</v>
+        <v>6800732</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,44 +896,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126345194</v>
+        <v>126343824</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>78739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427762</v>
+        <v>427890</v>
       </c>
       <c r="R4" t="n">
-        <v>6800755</v>
+        <v>6800684</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,19 +1003,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126344188</v>
+        <v>126341663</v>
       </c>
       <c r="B5" t="n">
         <v>78739</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427801</v>
+        <v>427662</v>
       </c>
       <c r="R5" t="n">
-        <v>6800732</v>
+        <v>6800508</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,22 +1110,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126343824</v>
+        <v>126341708</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,37 +1133,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427890</v>
+        <v>427684</v>
       </c>
       <c r="R6" t="n">
-        <v>6800684</v>
+        <v>6800496</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,44 +1217,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126341663</v>
+        <v>126345194</v>
       </c>
       <c r="B7" t="n">
-        <v>78739</v>
+        <v>98278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427662</v>
+        <v>427762</v>
       </c>
       <c r="R7" t="n">
-        <v>6800508</v>
+        <v>6800755</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1657,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126344438</v>
+        <v>126342845</v>
       </c>
       <c r="B11" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,34 +1668,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427856</v>
+        <v>427760</v>
       </c>
       <c r="R11" t="n">
-        <v>6800771</v>
+        <v>6800662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,22 +1752,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126342845</v>
+        <v>126345835</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427760</v>
+        <v>427639</v>
       </c>
       <c r="R12" t="n">
-        <v>6800662</v>
+        <v>6800521</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126345835</v>
+        <v>126342517</v>
       </c>
       <c r="B13" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,21 +1882,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427639</v>
+        <v>427766</v>
       </c>
       <c r="R13" t="n">
-        <v>6800521</v>
+        <v>6800601</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,19 +1966,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126342517</v>
+        <v>126343943</v>
       </c>
       <c r="B14" t="n">
         <v>78980</v>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427766</v>
+        <v>427824</v>
       </c>
       <c r="R14" t="n">
-        <v>6800601</v>
+        <v>6800762</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,22 +2073,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126343943</v>
+        <v>126345366</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,37 +2096,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427824</v>
+        <v>427713</v>
       </c>
       <c r="R15" t="n">
-        <v>6800762</v>
+        <v>6800676</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,22 +2180,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126345366</v>
+        <v>126344438</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>79569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,21 +2203,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427713</v>
+        <v>427856</v>
       </c>
       <c r="R16" t="n">
-        <v>6800676</v>
+        <v>6800771</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2941,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126342209</v>
+        <v>126342716</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427748</v>
+        <v>427772</v>
       </c>
       <c r="R23" t="n">
-        <v>6800537</v>
+        <v>6800647</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,22 +3036,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126342782</v>
+        <v>126343564</v>
       </c>
       <c r="B24" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427807</v>
+        <v>427718</v>
       </c>
       <c r="R24" t="n">
-        <v>6800637</v>
+        <v>6800610</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3143,19 +3143,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126342716</v>
+        <v>126344191</v>
       </c>
       <c r="B25" t="n">
         <v>78980</v>
@@ -3190,13 +3190,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427772</v>
+        <v>427863</v>
       </c>
       <c r="R25" t="n">
-        <v>6800647</v>
+        <v>6800776</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3262,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126343564</v>
+        <v>126342209</v>
       </c>
       <c r="B26" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,21 +3273,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427718</v>
+        <v>427748</v>
       </c>
       <c r="R26" t="n">
-        <v>6800610</v>
+        <v>6800537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3357,22 +3357,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126344191</v>
+        <v>126342782</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427863</v>
+        <v>427807</v>
       </c>
       <c r="R27" t="n">
-        <v>6800776</v>
+        <v>6800637</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3464,12 +3464,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126342821</v>
+        <v>126342348</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4236,37 +4236,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427757</v>
+        <v>427741</v>
       </c>
       <c r="R35" t="n">
-        <v>6800667</v>
+        <v>6800571</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4295,7 +4300,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4310,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,19 +4325,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126341773</v>
+        <v>126342821</v>
       </c>
       <c r="B36" t="n">
         <v>78980</v>
@@ -4363,14 +4368,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427709</v>
+        <v>427757</v>
       </c>
       <c r="R36" t="n">
-        <v>6800521</v>
+        <v>6800667</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4402,7 +4407,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4417,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,22 +4432,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126342373</v>
+        <v>126341773</v>
       </c>
       <c r="B37" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,34 +4455,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427751</v>
+        <v>427709</v>
       </c>
       <c r="R37" t="n">
-        <v>6800599</v>
+        <v>6800521</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4509,7 +4514,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4524,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,22 +4539,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126342562</v>
+        <v>126342373</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,21 +4562,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4581,13 +4586,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427775</v>
+        <v>427751</v>
       </c>
       <c r="R38" t="n">
-        <v>6800618</v>
+        <v>6800599</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4616,7 +4621,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4631,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4641,22 +4646,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126342348</v>
+        <v>126342562</v>
       </c>
       <c r="B39" t="n">
-        <v>57817</v>
+        <v>78980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,42 +4669,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427741</v>
+        <v>427775</v>
       </c>
       <c r="R39" t="n">
-        <v>6800571</v>
+        <v>6800618</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,12 +4753,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126343866</v>
+        <v>126343534</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7043,21 +7043,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427807</v>
+        <v>427760</v>
       </c>
       <c r="R61" t="n">
-        <v>6800637</v>
+        <v>6800856</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7127,19 +7127,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126342537</v>
+        <v>126343866</v>
       </c>
       <c r="B62" t="n">
         <v>78980</v>
@@ -7170,14 +7170,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427779</v>
+        <v>427807</v>
       </c>
       <c r="R62" t="n">
-        <v>6800578</v>
+        <v>6800637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7234,22 +7234,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126343534</v>
+        <v>126342537</v>
       </c>
       <c r="B63" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7257,34 +7257,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427760</v>
+        <v>427779</v>
       </c>
       <c r="R63" t="n">
-        <v>6800856</v>
+        <v>6800578</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7341,12 +7341,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126345319</v>
+        <v>126342196</v>
       </c>
       <c r="B8" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,34 +1347,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427713</v>
+        <v>427721</v>
       </c>
       <c r="R8" t="n">
-        <v>6800676</v>
+        <v>6800575</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,22 +1431,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126342196</v>
+        <v>126344155</v>
       </c>
       <c r="B9" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427721</v>
+        <v>427791</v>
       </c>
       <c r="R9" t="n">
-        <v>6800575</v>
+        <v>6800750</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,22 +1538,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126344155</v>
+        <v>126345319</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,37 +1561,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427791</v>
+        <v>427713</v>
       </c>
       <c r="R10" t="n">
-        <v>6800750</v>
+        <v>6800676</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126342348</v>
+        <v>126342821</v>
       </c>
       <c r="B35" t="n">
-        <v>57817</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4236,42 +4236,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427741</v>
+        <v>427757</v>
       </c>
       <c r="R35" t="n">
-        <v>6800571</v>
+        <v>6800667</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4300,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4310,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4325,19 +4320,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126342821</v>
+        <v>126341773</v>
       </c>
       <c r="B36" t="n">
         <v>78980</v>
@@ -4368,14 +4363,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427757</v>
+        <v>427709</v>
       </c>
       <c r="R36" t="n">
-        <v>6800667</v>
+        <v>6800521</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4407,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4417,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4432,22 +4427,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126341773</v>
+        <v>126342373</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4455,34 +4450,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427709</v>
+        <v>427751</v>
       </c>
       <c r="R37" t="n">
-        <v>6800521</v>
+        <v>6800599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4514,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4524,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4539,22 +4534,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126342373</v>
+        <v>126342562</v>
       </c>
       <c r="B38" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,21 +4557,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4586,13 +4581,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427751</v>
+        <v>427775</v>
       </c>
       <c r="R38" t="n">
-        <v>6800599</v>
+        <v>6800618</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4621,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4631,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4646,22 +4641,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126342562</v>
+        <v>126342348</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4669,37 +4664,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427775</v>
+        <v>427741</v>
       </c>
       <c r="R39" t="n">
-        <v>6800618</v>
+        <v>6800571</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,12 +4753,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126343534</v>
+        <v>126343866</v>
       </c>
       <c r="B61" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7043,21 +7043,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427760</v>
+        <v>427807</v>
       </c>
       <c r="R61" t="n">
-        <v>6800856</v>
+        <v>6800637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7127,19 +7127,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126343866</v>
+        <v>126342537</v>
       </c>
       <c r="B62" t="n">
         <v>78980</v>
@@ -7170,14 +7170,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427807</v>
+        <v>427779</v>
       </c>
       <c r="R62" t="n">
-        <v>6800637</v>
+        <v>6800578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7234,22 +7234,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126342537</v>
+        <v>126343534</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7257,34 +7257,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skrollhuvud, Dlr</t>
+          <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427779</v>
+        <v>427760</v>
       </c>
       <c r="R63" t="n">
-        <v>6800578</v>
+        <v>6800856</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7341,12 +7341,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -10466,45 +10466,59 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126360881</v>
+        <v>126360931</v>
       </c>
       <c r="B93" t="n">
-        <v>78739</v>
+        <v>98395</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>219874</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427452</v>
+        <v>427472</v>
       </c>
       <c r="R93" t="n">
-        <v>6800778</v>
+        <v>6800743</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10536,7 +10550,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10546,7 +10560,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10573,10 +10587,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126361181</v>
+        <v>126360881</v>
       </c>
       <c r="B94" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10584,21 +10598,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10608,13 +10622,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427489</v>
+        <v>427452</v>
       </c>
       <c r="R94" t="n">
-        <v>6800696</v>
+        <v>6800778</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10643,7 +10657,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10653,7 +10667,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10680,62 +10694,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126360931</v>
+        <v>126361181</v>
       </c>
       <c r="B95" t="n">
-        <v>98395</v>
+        <v>78980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skrollhuvud, Skrollhuvud, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427472</v>
+        <v>427489</v>
       </c>
       <c r="R95" t="n">
-        <v>6800743</v>
+        <v>6800696</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10898,10 +10898,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126377445</v>
+        <v>126377470</v>
       </c>
       <c r="B97" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10909,21 +10909,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10933,10 +10933,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427899</v>
+        <v>427902</v>
       </c>
       <c r="R97" t="n">
-        <v>6800814</v>
+        <v>6800821</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -10995,10 +10995,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126377448</v>
+        <v>126377504</v>
       </c>
       <c r="B98" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11006,21 +11006,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11030,10 +11030,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427957</v>
+        <v>427888</v>
       </c>
       <c r="R98" t="n">
-        <v>6800675</v>
+        <v>6800586</v>
       </c>
       <c r="S98" t="n">
         <v>1</v>
@@ -11092,10 +11092,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126377470</v>
+        <v>126377445</v>
       </c>
       <c r="B99" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11103,21 +11103,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427902</v>
+        <v>427899</v>
       </c>
       <c r="R99" t="n">
-        <v>6800821</v>
+        <v>6800814</v>
       </c>
       <c r="S99" t="n">
         <v>1</v>
@@ -11189,10 +11189,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126377504</v>
+        <v>126377448</v>
       </c>
       <c r="B100" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11200,21 +11200,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11224,10 +11224,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427888</v>
+        <v>427957</v>
       </c>
       <c r="R100" t="n">
-        <v>6800586</v>
+        <v>6800675</v>
       </c>
       <c r="S100" t="n">
         <v>1</v>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -14278,7 +14278,7 @@
         <v>126344242</v>
       </c>
       <c r="B131" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -14278,7 +14278,7 @@
         <v>126344242</v>
       </c>
       <c r="B131" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -14171,7 +14171,7 @@
         <v>126342041</v>
       </c>
       <c r="B130" t="n">
-        <v>56840</v>
+        <v>56844</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>126344242</v>
       </c>
       <c r="B131" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -14171,7 +14171,7 @@
         <v>126342041</v>
       </c>
       <c r="B130" t="n">
-        <v>56844</v>
+        <v>56846</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>126344242</v>
       </c>
       <c r="B131" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 30028-2025 artfynd.xlsx
+++ b/artfynd/A 30028-2025 artfynd.xlsx
@@ -14171,7 +14171,7 @@
         <v>126342041</v>
       </c>
       <c r="B130" t="n">
-        <v>56846</v>
+        <v>56849</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>126344242</v>
       </c>
       <c r="B131" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
